--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE182"/>
+  <dimension ref="A1:AE183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>44456</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 7821-2024</t>
+          <t>A 45507-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45349</v>
+        <v>45578</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1440,22 +1440,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1464,819 +1464,817 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Knärot
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 7821-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>7</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Slåtterfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35828-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45532</v>
-      </c>
-      <c r="E10" s="1" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 37686-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 45507-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45578</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Knärot
-Lönnlav</t>
-        </is>
-      </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
+          <t>A 35828-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45532</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>A 55897-2021</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>44476</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>4.3</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55897-2021 artfynd.xlsx", "A 55897-2021")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55897-2021 karta.png", "A 55897-2021")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55897-2021 georefererad karta.tif", "A 55897-2021")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55897-2021 FSC-klagomål.docx", "A 55897-2021")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55897-2021 FSC-klagomål mail.docx", "A 55897-2021")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55897-2021 tillsynsbegäran.docx", "A 55897-2021")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55897-2021 tillsynsbegäran mail.docx", "A 55897-2021")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/A 55897-2021 prioriterade fågelarter.docx", "A 55897-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 7817-2024</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45349</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>8.9</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Ask
 Huskvarnafibbla</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7817-2024 artfynd.xlsx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7817-2024 karta.png", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7817-2024 georefererad karta.tif", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7817-2024 FSC-klagomål.docx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7817-2024 FSC-klagomål mail.docx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7817-2024 tillsynsbegäran.docx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7817-2024 tillsynsbegäran mail.docx", "A 7817-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 7365-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>44971</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>1.6</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7365-2023 artfynd.xlsx", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7365-2023 karta.png", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7365-2023 georefererad karta.tif", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7365-2023 FSC-klagomål.docx", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7365-2023 FSC-klagomål mail.docx", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7365-2023 tillsynsbegäran.docx", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7365-2023 tillsynsbegäran mail.docx", "A 7365-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>S 3854-2022</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>44747</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>45.6</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Pärluggla
 Orre</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/S 3854-2022 artfynd.xlsx", "S 3854-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/S 3854-2022 karta.png", "S 3854-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/S 3854-2022 georefererad karta.tif", "S 3854-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/S 3854-2022 FSC-klagomål.docx", "S 3854-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/S 3854-2022 FSC-klagomål mail.docx", "S 3854-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/S 3854-2022 tillsynsbegäran.docx", "S 3854-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/S 3854-2022 tillsynsbegäran mail.docx", "S 3854-2022")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/S 3854-2022 prioriterade fågelarter.docx", "S 3854-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 47692-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44854</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 47692-2022 artfynd.xlsx", "A 47692-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 47692-2022 karta.png", "A 47692-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 47692-2022 georefererad karta.tif", "A 47692-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 47692-2022 FSC-klagomål.docx", "A 47692-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 47692-2022 FSC-klagomål mail.docx", "A 47692-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 47692-2022 tillsynsbegäran.docx", "A 47692-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 47692-2022 tillsynsbegäran mail.docx", "A 47692-2022")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/A 47692-2022 prioriterade fågelarter.docx", "A 47692-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 47692-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2290,10 +2288,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44846</v>
+        <v>44854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,10 +2304,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2318,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2330,10 +2328,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2342,46 +2340,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 47692-2022 artfynd.xlsx", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 47692-2022 karta.png", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 47692-2022 georefererad karta.tif", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 47692-2022 FSC-klagomål.docx", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 47692-2022 FSC-klagomål mail.docx", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 47692-2022 tillsynsbegäran.docx", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 47692-2022 tillsynsbegäran mail.docx", "A 47692-2022")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/A 47692-2022 prioriterade fågelarter.docx", "A 47692-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2395,10 +2397,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45349</v>
+        <v>45393</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2411,16 +2413,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2435,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2451,42 +2453,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 62232-2022</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2500,10 +2502,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44922</v>
+        <v>46031</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,8 +2517,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2525,13 +2532,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2543,55 +2550,55 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2605,10 +2612,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45401</v>
+        <v>44890</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2626,7 +2633,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2638,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2650,10 +2657,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2666,46 +2673,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2715,14 +2718,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45972</v>
+        <v>45401</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2734,11 +2737,16 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2747,10 +2755,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2768,42 +2776,46 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
@@ -2827,7 +2839,7 @@
         <v>46122</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2915,7 +2927,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2925,14 +2937,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44890</v>
+        <v>45972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2944,29 +2956,24 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
@@ -2974,58 +2981,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3046,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45393</v>
+        <v>45349</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,17 +3062,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3079,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3095,42 +3102,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3144,10 +3151,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46031</v>
+        <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3159,13 +3166,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3174,10 +3176,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3192,55 +3194,55 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 62232-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3254,10 +3256,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45629</v>
+        <v>44922</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3269,13 +3271,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3284,13 +3281,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3302,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3315,42 +3312,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3364,10 +3361,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45007</v>
+        <v>45629</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3379,18 +3376,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3404,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3416,46 +3418,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3469,10 +3471,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45189</v>
+        <v>45007</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3484,25 +3486,20 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3514,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3530,59 +3527,59 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S 694-2026</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46091</v>
+        <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3594,21 +3591,26 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>59.7</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3619,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3631,67 +3633,63 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/S 694-2026 artfynd.xlsx", "S 694-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/S 694-2026 karta.png", "S 694-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/S 694-2026 georefererad karta.tif", "S 694-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/S 694-2026 FSC-klagomål.docx", "S 694-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/S 694-2026 FSC-klagomål mail.docx", "S 694-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/S 694-2026 tillsynsbegäran.docx", "S 694-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/S 694-2026 tillsynsbegäran mail.docx", "S 694-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/S 694-2026 prioriterade fågelarter.docx", "S 694-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55888-2021</t>
+          <t>S 694-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44476</v>
+        <v>46091</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3704,10 +3702,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>59.7</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3734,20 +3732,56 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/S 694-2026 artfynd.xlsx", "S 694-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/S 694-2026 karta.png", "S 694-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/S 694-2026 georefererad karta.tif", "S 694-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/S 694-2026 FSC-klagomål.docx", "S 694-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/S 694-2026 FSC-klagomål mail.docx", "S 694-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/S 694-2026 tillsynsbegäran.docx", "S 694-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/S 694-2026 tillsynsbegäran mail.docx", "S 694-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/S 694-2026 prioriterade fågelarter.docx", "S 694-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 65493-2021</t>
+          <t>A 55888-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3761,10 +3795,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44516</v>
+        <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3776,13 +3810,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3825,7 +3854,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 39354-2022</t>
+          <t>A 65493-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3839,10 +3868,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44817</v>
+        <v>44516</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3854,8 +3883,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3898,7 +3932,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 52062-2022</t>
+          <t>A 39354-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3908,14 +3942,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44873</v>
+        <v>44817</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3928,7 +3962,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3971,7 +4005,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52058-2022</t>
+          <t>A 52062-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3988,7 +4022,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4001,7 +4035,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4044,7 +4078,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55896-2021</t>
+          <t>A 52058-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4054,14 +4088,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44476</v>
+        <v>44873</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4074,7 +4108,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4117,7 +4151,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57229-2021</t>
+          <t>A 55896-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4131,10 +4165,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44483</v>
+        <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4147,7 +4181,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4190,7 +4224,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9903-2022</t>
+          <t>A 57229-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4204,10 +4238,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44620</v>
+        <v>44483</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4220,7 +4254,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>16.8</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4263,7 +4297,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13811-2022</t>
+          <t>A 9903-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4277,10 +4311,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44649</v>
+        <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4293,7 +4327,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>16.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4336,7 +4370,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62452-2021</t>
+          <t>A 13811-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4350,10 +4384,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44503</v>
+        <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4366,7 +4400,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4409,7 +4443,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27760-2022</t>
+          <t>A 62452-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4423,10 +4457,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44743</v>
+        <v>44503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4439,7 +4473,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4482,7 +4516,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21691-2022</t>
+          <t>A 27760-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4496,10 +4530,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44707</v>
+        <v>44743</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4512,7 +4546,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4555,7 +4589,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16133-2022</t>
+          <t>A 21691-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4569,10 +4603,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44665</v>
+        <v>44707</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4585,7 +4619,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4628,7 +4662,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21693-2022</t>
+          <t>A 16133-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4642,10 +4676,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44707</v>
+        <v>44665</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4658,7 +4692,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4701,7 +4735,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 21693-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4715,10 +4749,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45702</v>
+        <v>44707</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4731,7 +4765,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4774,7 +4808,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4788,10 +4822,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45702</v>
+        <v>45145</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4804,7 +4838,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4847,7 +4881,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4861,10 +4895,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44817</v>
+        <v>45682</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4877,7 +4911,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4920,7 +4954,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4930,14 +4964,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44832</v>
+        <v>44707</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4993,7 +5027,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5007,10 +5041,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45455</v>
+        <v>45543</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5023,7 +5057,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5066,7 +5100,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5080,10 +5114,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44895</v>
+        <v>45543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5096,7 +5130,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5139,7 +5173,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5149,14 +5183,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44869</v>
+        <v>45478</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5169,7 +5203,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>10.9</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5212,7 +5246,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5226,10 +5260,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45529</v>
+        <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5242,7 +5276,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5285,7 +5319,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5299,10 +5333,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45469</v>
+        <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5315,7 +5349,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5358,7 +5392,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5372,10 +5406,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45553</v>
+        <v>44964</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5388,7 +5422,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5431,7 +5465,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5445,10 +5479,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44889</v>
+        <v>45596</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5461,7 +5495,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5504,7 +5538,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5518,10 +5552,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44964</v>
+        <v>45797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5534,7 +5568,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5577,7 +5611,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33875-2024</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5591,10 +5625,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45521</v>
+        <v>45740</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5607,7 +5641,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5650,7 +5684,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5664,10 +5698,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45321</v>
+        <v>45797</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5680,7 +5714,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5723,7 +5757,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5733,14 +5767,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44896</v>
+        <v>46007</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5753,7 +5787,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5796,7 +5830,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5806,14 +5840,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45393</v>
+        <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5826,7 +5860,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5869,7 +5903,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5883,10 +5917,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44964</v>
+        <v>46009</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5899,7 +5933,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5942,7 +5976,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5956,10 +5990,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44964</v>
+        <v>45804</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5972,7 +6006,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6015,7 +6049,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6029,10 +6063,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44964</v>
+        <v>45748</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6045,7 +6079,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6088,7 +6122,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 33875-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6102,10 +6136,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45820</v>
+        <v>45521</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6118,7 +6152,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6161,7 +6195,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6175,10 +6209,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44670</v>
+        <v>45638</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6191,7 +6225,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6234,7 +6268,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6248,10 +6282,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45553</v>
+        <v>46031</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6264,7 +6298,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6307,7 +6341,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6321,10 +6355,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44656</v>
+        <v>45890</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6337,7 +6371,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6380,7 +6414,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6394,10 +6428,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45890</v>
+        <v>45553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6410,7 +6444,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.2</v>
+        <v>6.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6453,7 +6487,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6467,10 +6501,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44707</v>
+        <v>44966</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6483,7 +6517,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6526,7 +6560,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6540,10 +6574,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45596</v>
+        <v>45820</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6556,7 +6590,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>15.1</v>
+        <v>4.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6599,7 +6633,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6613,10 +6647,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45251</v>
+        <v>45904</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6628,8 +6662,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6672,7 +6711,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6686,10 +6725,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45904</v>
+        <v>45169</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6701,13 +6740,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6750,7 +6784,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6760,14 +6794,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44998</v>
+        <v>45529</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6780,7 +6814,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6840,7 +6874,7 @@
         <v>45909</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6896,7 +6930,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6910,10 +6944,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45875</v>
+        <v>45686</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6926,7 +6960,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6969,7 +7003,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6983,10 +7017,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45875</v>
+        <v>45926</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6999,7 +7033,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7042,7 +7076,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7056,10 +7090,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45877</v>
+        <v>45926</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7072,7 +7106,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7115,7 +7149,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 46533-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7129,10 +7163,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45877</v>
+        <v>45926</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7145,7 +7179,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7188,7 +7222,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46533-2025</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7202,10 +7236,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45926</v>
+        <v>45928</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7218,7 +7252,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7261,7 +7295,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7275,10 +7309,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45926</v>
+        <v>45495</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7291,7 +7325,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7334,7 +7368,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7348,10 +7382,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45926</v>
+        <v>45933</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7364,7 +7398,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7407,7 +7441,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7421,10 +7455,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45928</v>
+        <v>44742</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7437,7 +7471,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7480,7 +7514,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7494,10 +7528,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45638</v>
+        <v>45875</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7510,7 +7544,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7553,7 +7587,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7567,10 +7601,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44977</v>
+        <v>45940</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7583,7 +7617,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7626,7 +7660,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7640,10 +7674,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45933</v>
+        <v>45875</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7656,7 +7690,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7699,7 +7733,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7713,10 +7747,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45940</v>
+        <v>45877</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7729,7 +7763,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7772,7 +7806,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7786,10 +7820,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45204</v>
+        <v>45877</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7802,7 +7836,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7845,7 +7879,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7859,10 +7893,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45596</v>
+        <v>45702</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7875,7 +7909,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7935,7 +7969,7 @@
         <v>46088</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7991,7 +8025,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8005,10 +8039,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45953</v>
+        <v>45048</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8021,7 +8055,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8064,7 +8098,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8074,14 +8108,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45752</v>
+        <v>44964</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8094,7 +8128,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>9.6</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8137,7 +8171,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8151,10 +8185,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45169</v>
+        <v>44964</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8167,7 +8201,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8210,7 +8244,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8224,10 +8258,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45246</v>
+        <v>45953</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8240,7 +8274,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8283,7 +8317,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8297,10 +8331,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45016</v>
+        <v>45596</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8313,7 +8347,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>15.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8373,7 +8407,7 @@
         <v>46126</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8429,7 +8463,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8443,10 +8477,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44865</v>
+        <v>45553</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8459,7 +8493,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8502,7 +8536,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8512,14 +8546,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45752</v>
+        <v>45393</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8532,7 +8566,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8575,7 +8609,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8589,10 +8623,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45752</v>
+        <v>44896</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8605,7 +8639,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8648,7 +8682,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8662,10 +8696,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45752</v>
+        <v>44607</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8678,7 +8712,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8721,7 +8755,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8735,10 +8769,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45495</v>
+        <v>45676</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8751,7 +8785,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8794,7 +8828,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8804,14 +8838,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46007</v>
+        <v>44700</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8824,7 +8858,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8867,7 +8901,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8881,10 +8915,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45313</v>
+        <v>45820</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8897,7 +8931,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.5</v>
+        <v>7.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8940,7 +8974,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8954,10 +8988,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46009</v>
+        <v>45730</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8970,7 +9004,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9013,7 +9047,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9027,10 +9061,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45748</v>
+        <v>45446</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9043,7 +9077,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9086,7 +9120,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9100,10 +9134,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44607</v>
+        <v>44964</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9116,7 +9150,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9159,7 +9193,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9173,10 +9207,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45820</v>
+        <v>44964</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9189,7 +9223,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9232,7 +9266,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9246,10 +9280,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44954</v>
+        <v>45214</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9262,7 +9296,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9305,7 +9339,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9319,10 +9353,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46031</v>
+        <v>45083</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9335,7 +9369,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>13.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9378,7 +9412,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9392,10 +9426,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44992</v>
+        <v>45103</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9408,7 +9442,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9451,7 +9485,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9465,10 +9499,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44938</v>
+        <v>45145</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9481,7 +9515,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9524,7 +9558,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9538,10 +9572,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45145</v>
+        <v>45755</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9554,7 +9588,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9597,7 +9631,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 1489-2024</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9611,10 +9645,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45305</v>
+        <v>45755</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9627,7 +9661,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9670,7 +9704,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9684,10 +9718,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45730</v>
+        <v>45752</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9700,7 +9734,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9743,7 +9777,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9757,10 +9791,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45048</v>
+        <v>45752</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9773,7 +9807,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9816,7 +9850,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9830,10 +9864,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45401</v>
+        <v>45752</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9846,7 +9880,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9889,7 +9923,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9903,10 +9937,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45083</v>
+        <v>45201</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9919,7 +9953,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>13.1</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9962,7 +9996,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9976,10 +10010,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45543</v>
+        <v>46197</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9992,7 +10026,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10035,7 +10069,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10049,10 +10083,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45543</v>
+        <v>45169</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10065,7 +10099,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10108,7 +10142,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10122,10 +10156,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45752</v>
+        <v>46240</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10138,7 +10172,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10181,7 +10215,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10195,10 +10229,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45145</v>
+        <v>46197</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10211,7 +10245,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10254,7 +10288,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10268,10 +10302,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45201</v>
+        <v>44977</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10284,7 +10318,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10327,7 +10361,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10337,14 +10371,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45170</v>
+        <v>45752</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10357,7 +10391,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>9.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10400,7 +10434,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10414,10 +10448,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45371</v>
+        <v>46246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10430,7 +10464,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10473,7 +10507,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10487,10 +10521,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45682</v>
+        <v>46246</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10503,7 +10537,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10546,7 +10580,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10560,10 +10594,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45169</v>
+        <v>44670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10576,7 +10610,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10619,7 +10653,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10633,10 +10667,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45686</v>
+        <v>46216</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10649,7 +10683,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10692,7 +10726,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10706,10 +10740,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44656</v>
+        <v>46216</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10722,7 +10756,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10765,7 +10799,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10779,10 +10813,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44656</v>
+        <v>46260</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10795,7 +10829,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10838,7 +10872,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10852,10 +10886,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45214</v>
+        <v>46240</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10868,7 +10902,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10911,7 +10945,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10925,10 +10959,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45637</v>
+        <v>45313</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10941,7 +10975,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10984,7 +11018,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10998,10 +11032,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44670</v>
+        <v>45637</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11014,7 +11048,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11057,7 +11091,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11071,10 +11105,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45740</v>
+        <v>46268</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11087,7 +11121,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11130,7 +11164,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11144,10 +11178,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44796</v>
+        <v>46268</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11160,7 +11194,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11203,7 +11237,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11217,10 +11251,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45372</v>
+        <v>45455</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11232,13 +11266,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11281,7 +11310,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11295,10 +11324,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45313</v>
+        <v>46268</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11311,7 +11340,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11354,7 +11383,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11364,14 +11393,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44966</v>
+        <v>46274</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11384,7 +11413,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11427,7 +11456,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11437,14 +11466,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45478</v>
+        <v>45372</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11456,8 +11485,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11500,7 +11534,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11514,10 +11548,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46197</v>
+        <v>46232</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11530,7 +11564,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11573,7 +11607,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11587,10 +11621,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46197</v>
+        <v>45740</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11646,7 +11680,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11660,10 +11694,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45371</v>
+        <v>44970</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11673,6 +11707,11 @@
       <c r="G139" t="inlineStr">
         <is>
           <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -11715,11 +11754,31 @@
         <v>0</v>
       </c>
       <c r="V139" s="2" t="inlineStr"/>
+      <c r="Z139">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA139">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB139">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC139">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD139">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11733,10 +11792,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46240</v>
+        <v>44954</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11749,7 +11808,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11792,7 +11851,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11806,10 +11865,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44954</v>
+        <v>45313</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11822,7 +11881,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11865,7 +11924,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11879,10 +11938,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44993</v>
+        <v>44656</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11895,7 +11954,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11938,7 +11997,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11952,10 +12011,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44964</v>
+        <v>44817</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11968,7 +12027,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12011,7 +12070,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12025,10 +12084,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45450</v>
+        <v>44895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12041,7 +12100,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12084,7 +12143,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12098,10 +12157,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44970</v>
+        <v>45455</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12113,13 +12172,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12158,31 +12212,11 @@
         <v>0</v>
       </c>
       <c r="V145" s="2" t="inlineStr"/>
-      <c r="Z145">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA145">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB145">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC145">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD145">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 1489-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12196,10 +12230,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45103</v>
+        <v>45305</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12212,7 +12246,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12255,7 +12289,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12269,10 +12303,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46246</v>
+        <v>44869</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12285,7 +12319,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.5</v>
+        <v>10.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12328,7 +12362,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12342,10 +12376,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44538</v>
+        <v>44889</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12358,7 +12392,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.7</v>
+        <v>14.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12401,7 +12435,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12415,10 +12449,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46246</v>
+        <v>44954</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12431,7 +12465,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12474,7 +12508,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12484,14 +12518,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45244</v>
+        <v>44954</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12504,7 +12538,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12547,7 +12581,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12557,14 +12591,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45455</v>
+        <v>44998</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12577,7 +12611,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12620,7 +12654,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12634,10 +12668,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44954</v>
+        <v>44865</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12650,7 +12684,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12693,7 +12727,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12707,10 +12741,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44964</v>
+        <v>44993</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12766,7 +12800,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12776,14 +12810,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45755</v>
+        <v>45244</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12796,7 +12830,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12839,7 +12873,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12853,10 +12887,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45755</v>
+        <v>45702</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12869,7 +12903,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12912,7 +12946,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12926,10 +12960,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46216</v>
+        <v>44938</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12942,7 +12976,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12985,7 +13019,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12999,10 +13033,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46216</v>
+        <v>44796</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13015,7 +13049,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13058,7 +13092,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13072,10 +13106,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45446</v>
+        <v>44656</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13088,7 +13122,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13131,7 +13165,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13145,10 +13179,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46260</v>
+        <v>44656</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13161,7 +13195,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13204,7 +13238,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13218,10 +13252,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46240</v>
+        <v>45469</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13234,7 +13268,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13277,7 +13311,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13287,14 +13321,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45676</v>
+        <v>44832</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13307,7 +13341,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13350,7 +13384,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13364,10 +13398,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46268</v>
+        <v>45321</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13380,7 +13414,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13423,7 +13457,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13437,10 +13471,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46268</v>
+        <v>45170</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13453,7 +13487,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13496,7 +13530,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13510,10 +13544,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44742</v>
+        <v>45401</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13526,7 +13560,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13569,7 +13603,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13583,10 +13617,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46268</v>
+        <v>44992</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13642,7 +13676,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13656,10 +13690,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44700</v>
+        <v>45371</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13672,7 +13706,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13715,7 +13749,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13725,14 +13759,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46274</v>
+        <v>44952</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13745,7 +13779,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13788,7 +13822,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13802,10 +13836,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46232</v>
+        <v>45204</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13818,7 +13852,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13861,7 +13895,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13875,10 +13909,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44952</v>
+        <v>45450</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13891,7 +13925,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13934,7 +13968,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13948,10 +13982,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45280</v>
+        <v>45016</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13964,7 +13998,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14007,7 +14041,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14021,10 +14055,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45324</v>
+        <v>45752</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14037,7 +14071,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14080,7 +14114,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14094,10 +14128,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44593</v>
+        <v>45251</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14110,7 +14144,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14153,7 +14187,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14167,10 +14201,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45484</v>
+        <v>44670</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14183,7 +14217,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14226,7 +14260,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14240,10 +14274,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44964</v>
+        <v>45371</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14256,7 +14290,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14299,7 +14333,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14313,10 +14347,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45740</v>
+        <v>45246</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14329,7 +14363,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14372,7 +14406,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14386,10 +14420,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45797</v>
+        <v>45280</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14402,7 +14436,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14445,7 +14479,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14459,10 +14493,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45797</v>
+        <v>45324</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14475,7 +14509,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14518,7 +14552,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14532,10 +14566,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45740</v>
+        <v>44593</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14548,7 +14582,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14591,7 +14625,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14605,10 +14639,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45804</v>
+        <v>45484</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14621,7 +14655,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14664,24 +14698,24 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S 3179-2024</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45524</v>
+        <v>44964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14694,7 +14728,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14737,148 +14771,221 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
+          <t>S 3179-2024</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>45524</v>
+      </c>
+      <c r="E181" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182" ht="15" customHeight="1">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>S 4371-2024</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D181" s="1" t="n">
+      <c r="D182" s="1" t="n">
         <v>45587</v>
       </c>
-      <c r="E181" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I181" t="n">
+      <c r="E182" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
         <v>1.5</v>
       </c>
-      <c r="J181" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" t="n">
-        <v>0</v>
-      </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
-        <v>0</v>
-      </c>
-      <c r="V181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="n">
+        <v>0</v>
+      </c>
+      <c r="V182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>S 1255-2025</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D182" s="1" t="n">
+      <c r="D183" s="1" t="n">
         <v>45763</v>
       </c>
-      <c r="E182" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I182" t="n">
+      <c r="E183" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
         <v>35.7</v>
       </c>
-      <c r="J182" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" t="n">
-        <v>0</v>
-      </c>
-      <c r="M182" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="n">
-        <v>0</v>
-      </c>
-      <c r="T182" t="n">
-        <v>0</v>
-      </c>
-      <c r="U182" t="n">
-        <v>0</v>
-      </c>
-      <c r="V182" s="2" t="inlineStr"/>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="n">
+        <v>0</v>
+      </c>
+      <c r="V183" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>44456</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 45507-2024</t>
+          <t>A 35828-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45578</v>
+        <v>45532</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1440,19 +1440,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>6.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -1464,378 +1464,378 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 7821-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Slåtterfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 45507-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45578</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Knärot
 Lönnlav</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 7821-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 37686-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>7</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Slåtterfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 37686-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 35828-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45532</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Sommarfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
         <v>44476</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 7817-2024</t>
+          <t>A 7365-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45349</v>
+        <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,22 +1982,22 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.9</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2022,142 +2022,142 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Fläcknycklar
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7365-2023 artfynd.xlsx", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7365-2023 karta.png", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7365-2023 georefererad karta.tif", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7365-2023 FSC-klagomål.docx", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7365-2023 FSC-klagomål mail.docx", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7365-2023 tillsynsbegäran.docx", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7365-2023 tillsynsbegäran mail.docx", "A 7365-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 7817-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Huskvarnafibbla</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7817-2024 artfynd.xlsx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7817-2024 karta.png", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7817-2024 georefererad karta.tif", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7817-2024 FSC-klagomål.docx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7817-2024 FSC-klagomål mail.docx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7817-2024 tillsynsbegäran.docx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7817-2024 tillsynsbegäran mail.docx", "A 7817-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 7365-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7365-2023 artfynd.xlsx", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7365-2023 karta.png", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7365-2023 georefererad karta.tif", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7365-2023 FSC-klagomål.docx", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7365-2023 FSC-klagomål mail.docx", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7365-2023 tillsynsbegäran.docx", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7365-2023 tillsynsbegäran mail.docx", "A 7365-2023")</f>
         <v/>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         <v>44747</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>44854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,14 +2393,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45393</v>
+        <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2413,20 +2413,20 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2449,46 +2449,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2498,14 +2498,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46031</v>
+        <v>45349</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2517,13 +2517,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2556,49 +2551,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2608,14 +2603,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44890</v>
+        <v>46122</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,13 +2622,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2666,49 +2656,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 62232-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2722,10 +2712,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45401</v>
+        <v>44922</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2737,28 +2727,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2779,50 +2764,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2832,14 +2813,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46122</v>
+        <v>45972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,23 +2833,23 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -2876,58 +2857,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2937,14 +2918,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45972</v>
+        <v>44890</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,11 +2937,16 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2972,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2981,58 +2967,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3042,14 +3028,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45349</v>
+        <v>46031</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,8 +3047,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3095,49 +3086,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3147,14 +3138,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44846</v>
+        <v>45393</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3167,19 +3158,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3191,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3203,46 +3194,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62232-2022</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3256,10 +3247,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44922</v>
+        <v>45629</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,8 +3262,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3281,13 +3277,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3299,7 +3295,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3312,42 +3308,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3361,10 +3357,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45629</v>
+        <v>45007</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3376,22 +3372,17 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3406,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3418,46 +3409,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3471,10 +3462,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45007</v>
+        <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3486,21 +3477,26 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3511,10 +3507,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3527,42 +3523,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3576,10 +3572,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45189</v>
+        <v>45401</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3593,14 +3589,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3637,35 +3633,39 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
         <v>46091</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44516</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44817</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44873</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>44483</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>44503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27760-2022</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44743</v>
+        <v>45740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21691-2022</t>
+          <t>A 27760-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44707</v>
+        <v>44743</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16133-2022</t>
+          <t>A 21691-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44665</v>
+        <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21693-2022</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44707</v>
+        <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 16133-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45145</v>
+        <v>44665</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45682</v>
+        <v>45702</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 21693-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4971,7 +4971,7 @@
         <v>44707</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45543</v>
+        <v>45875</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45543</v>
+        <v>45875</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45478</v>
+        <v>45702</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44538</v>
+        <v>45877</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44964</v>
+        <v>45877</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44964</v>
+        <v>44796</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5475,14 +5475,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45596</v>
+        <v>44832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45797</v>
+        <v>45455</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45740</v>
+        <v>45372</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5640,8 +5640,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5684,7 +5689,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5698,10 +5703,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45797</v>
+        <v>45313</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5714,7 +5719,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5757,7 +5762,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5767,14 +5772,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46007</v>
+        <v>44895</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5787,7 +5792,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5830,7 +5835,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5844,10 +5849,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45740</v>
+        <v>44964</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5860,7 +5865,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5903,7 +5908,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5917,10 +5922,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46009</v>
+        <v>44964</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5933,7 +5938,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5976,7 +5981,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5990,10 +5995,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45804</v>
+        <v>44964</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6006,7 +6011,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6049,7 +6054,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6063,10 +6068,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45748</v>
+        <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6079,7 +6084,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>10.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6122,7 +6127,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33875-2024</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6136,10 +6141,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45521</v>
+        <v>45469</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6152,7 +6157,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6195,7 +6200,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6209,10 +6214,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45638</v>
+        <v>45529</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6225,7 +6230,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6268,7 +6273,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6282,10 +6287,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46031</v>
+        <v>45890</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6298,7 +6303,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6341,7 +6346,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6351,14 +6356,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45890</v>
+        <v>46088</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6371,7 +6376,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6431,7 +6436,7 @@
         <v>45553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6487,7 +6492,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6501,10 +6506,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44966</v>
+        <v>44889</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6517,7 +6522,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>14.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6560,7 +6565,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 33875-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6574,10 +6579,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45820</v>
+        <v>45521</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6590,7 +6595,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6633,7 +6638,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6647,10 +6652,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45904</v>
+        <v>44964</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6662,13 +6667,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45169</v>
+        <v>45904</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6740,8 +6740,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6784,7 +6789,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6798,10 +6803,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45529</v>
+        <v>45321</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6814,7 +6819,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6857,7 +6862,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43134-2025</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6871,10 +6876,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45909</v>
+        <v>44896</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6887,7 +6892,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6930,7 +6935,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6940,14 +6945,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45686</v>
+        <v>45393</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6960,7 +6965,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7003,7 +7008,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 43134-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7017,10 +7022,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45926</v>
+        <v>45909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7033,7 +7038,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7076,7 +7081,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7090,10 +7095,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45926</v>
+        <v>44966</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7106,7 +7111,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7166,7 +7171,7 @@
         <v>45926</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7222,7 +7227,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7232,14 +7237,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45928</v>
+        <v>45478</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7252,7 +7257,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7295,7 +7300,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7309,10 +7314,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45495</v>
+        <v>45926</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7325,7 +7330,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7368,7 +7373,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7382,10 +7387,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45933</v>
+        <v>44670</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7398,7 +7403,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7441,7 +7446,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7455,10 +7460,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44742</v>
+        <v>45553</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7471,7 +7476,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7514,7 +7519,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7528,10 +7533,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45875</v>
+        <v>45926</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7544,7 +7549,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7587,7 +7592,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7601,10 +7606,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45940</v>
+        <v>45928</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7617,7 +7622,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7660,7 +7665,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7670,14 +7675,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45875</v>
+        <v>46126</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7690,7 +7695,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7733,7 +7738,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7747,10 +7752,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45877</v>
+        <v>45933</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7763,7 +7768,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7806,7 +7811,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7820,10 +7825,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45877</v>
+        <v>45371</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7836,7 +7841,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7879,7 +7884,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7893,10 +7898,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45702</v>
+        <v>45940</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7909,7 +7914,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7952,7 +7957,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7962,14 +7967,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46088</v>
+        <v>44656</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7982,7 +7987,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8025,7 +8030,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8039,10 +8044,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45048</v>
+        <v>44954</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8055,7 +8060,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8098,7 +8103,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44964</v>
+        <v>44707</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8128,7 +8133,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8171,7 +8176,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8185,10 +8190,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44964</v>
+        <v>45953</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8201,7 +8206,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8244,7 +8249,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8258,10 +8263,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45953</v>
+        <v>45596</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8274,7 +8279,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>15.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8317,7 +8322,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8331,10 +8336,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45596</v>
+        <v>44607</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8347,7 +8352,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>15.1</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8390,7 +8395,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8400,14 +8405,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46126</v>
+        <v>45820</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8420,7 +8425,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8463,7 +8468,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8477,10 +8482,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45553</v>
+        <v>44993</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8493,7 +8498,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8536,7 +8541,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8546,14 +8551,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45393</v>
+        <v>45251</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8566,7 +8571,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8609,7 +8614,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8619,14 +8624,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44896</v>
+        <v>44998</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8639,7 +8644,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8682,7 +8687,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8696,10 +8701,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44607</v>
+        <v>44964</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8712,7 +8717,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8755,7 +8760,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8769,10 +8774,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45676</v>
+        <v>45450</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8785,7 +8790,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8828,7 +8833,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8842,10 +8847,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44700</v>
+        <v>45730</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8858,7 +8863,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8901,7 +8906,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8915,10 +8920,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45820</v>
+        <v>45638</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8931,7 +8936,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8974,7 +8979,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8988,10 +8993,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45730</v>
+        <v>44977</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9004,7 +9009,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9047,7 +9052,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9061,10 +9066,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45446</v>
+        <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9076,8 +9081,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9116,11 +9126,31 @@
         <v>0</v>
       </c>
       <c r="V103" s="2" t="inlineStr"/>
+      <c r="Z103">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA103">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB103">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC103">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD103">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9134,10 +9164,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44964</v>
+        <v>45103</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9150,7 +9180,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9193,7 +9223,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9207,10 +9237,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44964</v>
+        <v>44538</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9223,7 +9253,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9266,7 +9296,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9280,10 +9310,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45214</v>
+        <v>45083</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9296,7 +9326,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.3</v>
+        <v>13.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9339,7 +9369,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9353,10 +9383,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45083</v>
+        <v>45204</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9369,7 +9399,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>13.1</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9412,7 +9442,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9426,10 +9456,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45103</v>
+        <v>45596</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9442,7 +9472,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9485,7 +9515,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9495,14 +9525,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45145</v>
+        <v>46007</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9515,7 +9545,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9558,7 +9588,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9572,10 +9602,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45755</v>
+        <v>46009</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9588,7 +9618,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9631,7 +9661,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9645,10 +9675,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45755</v>
+        <v>45748</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9704,7 +9734,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9714,14 +9744,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45752</v>
+        <v>45244</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9734,7 +9764,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9777,7 +9807,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9787,14 +9817,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
         <v>45752</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9807,7 +9837,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9850,7 +9880,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9864,10 +9894,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45752</v>
+        <v>45169</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9880,7 +9910,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9923,7 +9953,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9937,10 +9967,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45201</v>
+        <v>45246</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9953,7 +9983,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9996,7 +10026,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10010,10 +10040,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46197</v>
+        <v>46031</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10026,7 +10056,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10069,7 +10099,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10083,10 +10113,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45169</v>
+        <v>45455</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10099,7 +10129,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10142,7 +10172,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10156,10 +10186,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46240</v>
+        <v>45016</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10172,7 +10202,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10215,7 +10245,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10229,10 +10259,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46197</v>
+        <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10245,7 +10275,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10288,7 +10318,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10302,10 +10332,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44977</v>
+        <v>45752</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10318,7 +10348,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10361,7 +10391,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10371,14 +10401,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
         <v>45752</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10391,7 +10421,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10434,7 +10464,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10448,10 +10478,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46246</v>
+        <v>45752</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10464,7 +10494,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10507,7 +10537,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10521,10 +10551,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46246</v>
+        <v>45495</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10537,7 +10567,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10580,7 +10610,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10594,10 +10624,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44670</v>
+        <v>45313</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10610,7 +10640,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10653,7 +10683,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10667,10 +10697,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46216</v>
+        <v>44954</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10683,7 +10713,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10726,7 +10756,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10740,10 +10770,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46216</v>
+        <v>44954</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10756,7 +10786,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10799,7 +10829,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10813,10 +10843,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46260</v>
+        <v>44992</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10829,7 +10859,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10872,7 +10902,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10886,10 +10916,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46240</v>
+        <v>44964</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10902,7 +10932,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10945,7 +10975,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10959,10 +10989,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45313</v>
+        <v>44938</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10975,7 +11005,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11018,7 +11048,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11032,10 +11062,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45637</v>
+        <v>45145</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11048,7 +11078,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11091,7 +11121,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11105,10 +11135,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46268</v>
+        <v>45755</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11121,7 +11151,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11164,7 +11194,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11178,10 +11208,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46268</v>
+        <v>45755</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11194,7 +11224,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11237,7 +11267,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 1489-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11251,10 +11281,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45455</v>
+        <v>45305</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11267,7 +11297,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11310,7 +11340,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11324,10 +11354,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46268</v>
+        <v>46197</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11340,7 +11370,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11383,7 +11413,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11393,14 +11423,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46274</v>
+        <v>46197</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11413,7 +11443,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11456,7 +11486,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11470,10 +11500,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45372</v>
+        <v>46240</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11485,13 +11515,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11534,7 +11559,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11548,10 +11573,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46232</v>
+        <v>45446</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11564,7 +11589,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11607,7 +11632,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11621,10 +11646,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45740</v>
+        <v>45048</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11637,7 +11662,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11680,7 +11705,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11694,10 +11719,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44970</v>
+        <v>45401</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11709,13 +11734,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11754,31 +11774,11 @@
         <v>0</v>
       </c>
       <c r="V139" s="2" t="inlineStr"/>
-      <c r="Z139">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA139">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB139">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC139">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD139">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44954</v>
+        <v>46246</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11851,7 +11851,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11865,10 +11865,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45313</v>
+        <v>46246</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11938,10 +11938,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44656</v>
+        <v>45543</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11997,7 +11997,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44817</v>
+        <v>45543</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12070,7 +12070,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12084,10 +12084,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44895</v>
+        <v>45752</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12157,10 +12157,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45455</v>
+        <v>45676</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12216,7 +12216,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1489-2024</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45305</v>
+        <v>45145</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12289,7 +12289,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12303,10 +12303,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44869</v>
+        <v>45201</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44889</v>
+        <v>45170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>14.1</v>
+        <v>2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12435,7 +12435,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44954</v>
+        <v>45371</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12508,7 +12508,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44954</v>
+        <v>45682</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12581,7 +12581,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12591,14 +12591,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44998</v>
+        <v>45169</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12654,7 +12654,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12668,10 +12668,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44865</v>
+        <v>45686</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12727,7 +12727,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12741,10 +12741,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44993</v>
+        <v>46216</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12800,7 +12800,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12810,14 +12810,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45244</v>
+        <v>44656</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12873,7 +12873,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12887,10 +12887,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45702</v>
+        <v>44656</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12960,10 +12960,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44938</v>
+        <v>45214</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13019,7 +13019,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13033,10 +13033,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44796</v>
+        <v>45637</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13092,7 +13092,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13106,10 +13106,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44656</v>
+        <v>46216</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13165,7 +13165,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13179,10 +13179,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44656</v>
+        <v>44670</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13238,7 +13238,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13252,10 +13252,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45469</v>
+        <v>46260</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13311,7 +13311,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13321,14 +13321,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44832</v>
+        <v>46240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13384,7 +13384,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13398,10 +13398,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45321</v>
+        <v>46268</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13457,7 +13457,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45170</v>
+        <v>44742</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13530,7 +13530,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13544,10 +13544,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45401</v>
+        <v>46268</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13603,7 +13603,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13617,10 +13617,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44992</v>
+        <v>44700</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13676,7 +13676,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13690,10 +13690,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45371</v>
+        <v>46268</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13766,7 +13766,7 @@
         <v>44952</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13836,10 +13836,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45204</v>
+        <v>46232</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13895,7 +13895,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13905,14 +13905,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45450</v>
+        <v>46274</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13968,7 +13968,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13982,10 +13982,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45016</v>
+        <v>45280</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14041,7 +14041,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45752</v>
+        <v>45324</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14114,7 +14114,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14128,10 +14128,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45251</v>
+        <v>44593</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14187,7 +14187,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44670</v>
+        <v>45484</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14274,10 +14274,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45371</v>
+        <v>44964</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14333,7 +14333,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14347,10 +14347,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45246</v>
+        <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14420,10 +14420,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45280</v>
+        <v>45797</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14479,7 +14479,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14493,10 +14493,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45324</v>
+        <v>45797</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14552,7 +14552,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14566,10 +14566,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44593</v>
+        <v>45740</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14625,7 +14625,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14639,10 +14639,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45484</v>
+        <v>45804</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14698,7 +14698,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14712,10 +14712,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44964</v>
+        <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14788,7 +14788,7 @@
         <v>45524</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45587</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45763</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>44456</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45173</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 35828-2024</t>
+          <t>A 45507-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45532</v>
+        <v>45578</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1440,19 +1440,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.7</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -1464,271 +1464,271 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Knärot
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 7821-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Slåtterfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 35828-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45532</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 7821-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>7</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Slåtterfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 45507-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45578</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Knärot
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>44476</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 7365-2023</t>
+          <t>A 7817-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44971</v>
+        <v>45349</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,34 +1982,34 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>8.9</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2022,142 +2022,142 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Huskvarnafibbla</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7817-2024 artfynd.xlsx", "A 7817-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7817-2024 karta.png", "A 7817-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7817-2024 georefererad karta.tif", "A 7817-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7817-2024 FSC-klagomål.docx", "A 7817-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7817-2024 FSC-klagomål mail.docx", "A 7817-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7817-2024 tillsynsbegäran.docx", "A 7817-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7817-2024 tillsynsbegäran mail.docx", "A 7817-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 7365-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44971</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Fläcknycklar
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7365-2023 artfynd.xlsx", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7365-2023 karta.png", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7365-2023 georefererad karta.tif", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7365-2023 FSC-klagomål.docx", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7365-2023 FSC-klagomål mail.docx", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7365-2023 tillsynsbegäran.docx", "A 7365-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7365-2023 tillsynsbegäran mail.docx", "A 7365-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 7817-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Huskvarnafibbla</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7817-2024 artfynd.xlsx", "A 7817-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7817-2024 karta.png", "A 7817-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7817-2024 georefererad karta.tif", "A 7817-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7817-2024 FSC-klagomål.docx", "A 7817-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7817-2024 FSC-klagomål mail.docx", "A 7817-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7817-2024 tillsynsbegäran.docx", "A 7817-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7817-2024 tillsynsbegäran mail.docx", "A 7817-2024")</f>
         <v/>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         <v>44747</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>44854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2393,14 +2393,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44846</v>
+        <v>45393</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2413,19 +2413,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2449,46 +2449,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2498,14 +2498,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45349</v>
+        <v>46031</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2517,8 +2517,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2551,49 +2556,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2603,14 +2608,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46122</v>
+        <v>44890</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2622,8 +2627,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2656,49 +2666,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 62232-2022</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2712,10 +2722,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44922</v>
+        <v>45401</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2727,11 +2737,16 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2740,10 +2755,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2764,39 +2779,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
@@ -2820,7 +2839,7 @@
         <v>45972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2908,7 +2927,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2918,14 +2937,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44890</v>
+        <v>45349</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2937,23 +2956,18 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2967,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2979,46 +2993,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3028,14 +3042,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46031</v>
+        <v>46122</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,22 +3061,17 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3077,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3086,49 +3095,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3138,14 +3147,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45393</v>
+        <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3158,20 +3167,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3182,10 +3191,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3194,46 +3203,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 62232-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3247,10 +3256,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45629</v>
+        <v>44922</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3262,13 +3271,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3277,13 +3281,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3295,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3308,42 +3312,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3357,10 +3361,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45007</v>
+        <v>45629</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3372,18 +3376,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3397,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3409,46 +3418,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3462,10 +3471,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45189</v>
+        <v>45007</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3477,25 +3486,20 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3507,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3523,42 +3527,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3572,10 +3576,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45401</v>
+        <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3589,14 +3593,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3633,39 +3637,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
         <v>46091</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44516</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44817</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44873</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>44483</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>44503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 27760-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45740</v>
+        <v>44743</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27760-2022</t>
+          <t>A 21691-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44743</v>
+        <v>44707</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21691-2022</t>
+          <t>A 16133-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44707</v>
+        <v>44665</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 21693-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44817</v>
+        <v>44707</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16133-2022</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44665</v>
+        <v>45145</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45702</v>
+        <v>45682</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21693-2022</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4971,7 +4971,7 @@
         <v>44707</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45875</v>
+        <v>45543</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45875</v>
+        <v>45543</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45702</v>
+        <v>45478</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45877</v>
+        <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45877</v>
+        <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44796</v>
+        <v>44964</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5475,14 +5475,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44832</v>
+        <v>45596</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 33875-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45455</v>
+        <v>45521</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45372</v>
+        <v>45797</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5640,13 +5640,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5689,7 +5684,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5703,10 +5698,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45313</v>
+        <v>45638</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5719,7 +5714,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5762,7 +5757,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5776,10 +5771,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44895</v>
+        <v>45553</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5792,7 +5787,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5835,7 +5830,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5849,10 +5844,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44964</v>
+        <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5865,7 +5860,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5908,7 +5903,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5922,10 +5917,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44964</v>
+        <v>45797</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5938,7 +5933,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5981,7 +5976,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5995,10 +5990,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44964</v>
+        <v>45740</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6011,7 +6006,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6054,7 +6049,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44869</v>
+        <v>44966</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6084,7 +6079,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>10.9</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6127,7 +6122,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6141,10 +6136,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45469</v>
+        <v>45804</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6157,7 +6152,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6200,7 +6195,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6214,10 +6209,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45529</v>
+        <v>46031</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6230,7 +6225,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6273,7 +6268,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6287,10 +6282,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45890</v>
+        <v>45169</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6303,7 +6298,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6346,7 +6341,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6356,14 +6351,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46088</v>
+        <v>45529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6376,7 +6371,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6419,7 +6414,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6433,10 +6428,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45553</v>
+        <v>45890</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6449,7 +6444,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6492,7 +6487,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6506,10 +6501,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44889</v>
+        <v>45820</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6522,7 +6517,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>14.1</v>
+        <v>4.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6565,7 +6560,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 33875-2024</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6579,10 +6574,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45521</v>
+        <v>45686</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6595,7 +6590,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6638,7 +6633,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6652,10 +6647,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44964</v>
+        <v>45904</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6667,8 +6662,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45904</v>
+        <v>45495</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6740,13 +6740,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6789,7 +6784,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 43134-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6803,10 +6798,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45321</v>
+        <v>45909</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6819,7 +6814,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6862,7 +6857,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6876,10 +6871,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44896</v>
+        <v>44742</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6892,7 +6887,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6935,7 +6930,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6945,14 +6940,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45393</v>
+        <v>45702</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6965,7 +6960,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7008,7 +7003,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43134-2025</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7022,10 +7017,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45909</v>
+        <v>45926</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7038,7 +7033,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7081,7 +7076,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7095,10 +7090,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44966</v>
+        <v>45926</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7111,7 +7106,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7171,7 +7166,7 @@
         <v>45926</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7227,7 +7222,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7237,14 +7232,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45478</v>
+        <v>45928</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7257,7 +7252,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7300,7 +7295,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7314,10 +7309,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45926</v>
+        <v>45933</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7330,7 +7325,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7373,7 +7368,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7387,10 +7382,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44670</v>
+        <v>45048</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7403,7 +7398,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7446,7 +7441,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7460,10 +7455,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45553</v>
+        <v>45875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7476,7 +7471,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7519,7 +7514,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7533,10 +7528,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45926</v>
+        <v>45940</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7549,7 +7544,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7592,7 +7587,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7606,10 +7601,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45928</v>
+        <v>45875</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7622,7 +7617,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7665,7 +7660,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7675,14 +7670,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46126</v>
+        <v>44964</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7695,7 +7690,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7738,7 +7733,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7752,10 +7747,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45933</v>
+        <v>45877</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7768,7 +7763,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7811,7 +7806,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7825,10 +7820,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45371</v>
+        <v>45877</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7841,7 +7836,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7884,7 +7879,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7898,10 +7893,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45940</v>
+        <v>44964</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7914,7 +7909,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7957,7 +7952,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7971,10 +7966,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44656</v>
+        <v>45953</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8030,7 +8025,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8044,10 +8039,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44954</v>
+        <v>45596</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8060,7 +8055,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>15.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8103,7 +8098,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8117,10 +8112,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44707</v>
+        <v>45553</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8133,7 +8128,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8176,7 +8171,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8186,14 +8181,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45953</v>
+        <v>45393</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8206,7 +8201,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8249,7 +8244,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8263,10 +8258,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45596</v>
+        <v>44896</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8279,7 +8274,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>15.1</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8322,7 +8317,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8336,10 +8331,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44607</v>
+        <v>45676</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8352,7 +8347,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8395,7 +8390,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8409,10 +8404,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45820</v>
+        <v>44700</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8425,7 +8420,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.7</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8468,7 +8463,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8478,14 +8473,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44993</v>
+        <v>46088</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8498,7 +8493,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8541,7 +8536,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8555,10 +8550,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45251</v>
+        <v>45446</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8571,7 +8566,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8614,7 +8609,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8624,14 +8619,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44998</v>
+        <v>46007</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8644,7 +8639,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8687,7 +8682,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8701,10 +8696,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44964</v>
+        <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8717,7 +8712,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8760,7 +8755,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8774,10 +8769,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45450</v>
+        <v>44964</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8790,7 +8785,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8833,7 +8828,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8847,10 +8842,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45730</v>
+        <v>44964</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8863,7 +8858,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8906,7 +8901,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8920,10 +8915,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45638</v>
+        <v>45214</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8936,7 +8931,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8979,7 +8974,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8993,10 +8988,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44977</v>
+        <v>45748</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9009,7 +9004,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9052,7 +9047,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9066,10 +9061,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44970</v>
+        <v>45103</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9081,13 +9076,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9126,31 +9116,11 @@
         <v>0</v>
       </c>
       <c r="V103" s="2" t="inlineStr"/>
-      <c r="Z103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9164,10 +9134,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45103</v>
+        <v>45145</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9180,7 +9150,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9223,7 +9193,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9237,10 +9207,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44538</v>
+        <v>45755</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9253,7 +9223,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9296,7 +9266,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9310,10 +9280,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45083</v>
+        <v>45755</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9326,7 +9296,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>13.1</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9369,7 +9339,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9383,10 +9353,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45204</v>
+        <v>45752</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9399,7 +9369,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9442,7 +9412,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9456,10 +9426,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45596</v>
+        <v>45752</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9472,7 +9442,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9515,7 +9485,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9525,14 +9495,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46007</v>
+        <v>45752</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9545,7 +9515,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9588,7 +9558,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9602,10 +9572,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46009</v>
+        <v>45201</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9618,7 +9588,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9661,7 +9631,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9671,14 +9641,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45748</v>
+        <v>46126</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9691,7 +9661,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9734,7 +9704,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9744,14 +9714,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45244</v>
+        <v>45169</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9764,7 +9734,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9807,7 +9777,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9817,14 +9787,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45752</v>
+        <v>44977</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9837,7 +9807,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>9.6</v>
+        <v>4.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9880,7 +9850,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9890,14 +9860,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45169</v>
+        <v>45752</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9910,7 +9880,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>9.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9953,7 +9923,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9967,10 +9937,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45246</v>
+        <v>44607</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9983,7 +9953,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10026,7 +9996,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10040,10 +10010,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46031</v>
+        <v>44670</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10056,7 +10026,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10099,7 +10069,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10113,10 +10083,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45455</v>
+        <v>45313</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10129,7 +10099,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10172,7 +10142,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10186,10 +10156,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45016</v>
+        <v>45637</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10202,7 +10172,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10245,7 +10215,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10259,10 +10229,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44865</v>
+        <v>45820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10275,7 +10245,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10318,7 +10288,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10332,10 +10302,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45752</v>
+        <v>45730</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10348,7 +10318,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10391,7 +10361,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10405,10 +10375,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45752</v>
+        <v>45455</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10421,7 +10391,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10464,7 +10434,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10478,10 +10448,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45752</v>
+        <v>45083</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10494,7 +10464,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4</v>
+        <v>13.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10537,7 +10507,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10551,10 +10521,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45495</v>
+        <v>45372</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10566,8 +10536,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10610,7 +10585,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10624,10 +10599,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45313</v>
+        <v>45740</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10640,7 +10615,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10683,7 +10658,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10697,10 +10672,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44954</v>
+        <v>44970</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10712,8 +10687,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10752,11 +10732,31 @@
         <v>0</v>
       </c>
       <c r="V125" s="2" t="inlineStr"/>
+      <c r="Z125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10773,7 +10773,7 @@
         <v>44954</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44992</v>
+        <v>45313</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10902,7 +10902,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10916,10 +10916,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44964</v>
+        <v>44656</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10975,7 +10975,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10989,10 +10989,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44938</v>
+        <v>44817</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11048,7 +11048,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11062,10 +11062,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45145</v>
+        <v>44895</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11121,7 +11121,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11135,10 +11135,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45755</v>
+        <v>45455</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 1489-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11208,10 +11208,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45755</v>
+        <v>45305</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1489-2024</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11281,10 +11281,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45305</v>
+        <v>44869</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.1</v>
+        <v>10.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11354,10 +11354,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46197</v>
+        <v>44889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>14.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11413,7 +11413,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11427,10 +11427,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46197</v>
+        <v>44954</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11486,7 +11486,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11500,10 +11500,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46240</v>
+        <v>44954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11559,7 +11559,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11569,14 +11569,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45446</v>
+        <v>44998</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11632,7 +11632,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11646,10 +11646,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45048</v>
+        <v>44865</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11705,7 +11705,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45401</v>
+        <v>44993</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46246</v>
+        <v>45244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11851,7 +11851,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11865,10 +11865,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46246</v>
+        <v>45702</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11938,10 +11938,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45543</v>
+        <v>46197</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11997,7 +11997,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45543</v>
+        <v>44938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12070,7 +12070,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12084,10 +12084,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45752</v>
+        <v>44796</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12157,10 +12157,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45676</v>
+        <v>46240</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12216,7 +12216,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45145</v>
+        <v>46197</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12289,7 +12289,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12303,10 +12303,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45201</v>
+        <v>44656</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45170</v>
+        <v>44656</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12435,7 +12435,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45371</v>
+        <v>46246</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12508,7 +12508,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45682</v>
+        <v>45469</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12581,7 +12581,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12595,10 +12595,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45169</v>
+        <v>46246</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12654,7 +12654,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12664,14 +12664,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45686</v>
+        <v>44832</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12727,7 +12727,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12741,10 +12741,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46216</v>
+        <v>45321</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12800,7 +12800,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12814,10 +12814,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44656</v>
+        <v>45170</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12873,7 +12873,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12887,10 +12887,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44656</v>
+        <v>46216</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12960,10 +12960,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45214</v>
+        <v>46216</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13019,7 +13019,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13033,10 +13033,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45637</v>
+        <v>45401</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13092,7 +13092,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13106,10 +13106,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46216</v>
+        <v>44992</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13165,7 +13165,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13179,10 +13179,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44670</v>
+        <v>46260</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13238,7 +13238,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13252,10 +13252,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46260</v>
+        <v>45371</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13328,7 +13328,7 @@
         <v>46240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13398,10 +13398,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46268</v>
+        <v>44952</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13457,7 +13457,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44742</v>
+        <v>45204</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13530,7 +13530,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13544,10 +13544,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46268</v>
+        <v>45450</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13603,7 +13603,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13617,10 +13617,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44700</v>
+        <v>46268</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46268</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13763,10 +13763,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44952</v>
+        <v>45016</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13822,7 +13822,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13836,10 +13836,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46232</v>
+        <v>46268</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13895,7 +13895,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13905,14 +13905,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46274</v>
+        <v>45752</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13968,7 +13968,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13982,10 +13982,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45280</v>
+        <v>45251</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14041,7 +14041,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45324</v>
+        <v>44670</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14114,7 +14114,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14128,10 +14128,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44593</v>
+        <v>45371</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14187,7 +14187,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45484</v>
+        <v>46232</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14274,10 +14274,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44964</v>
+        <v>45246</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14333,7 +14333,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14343,14 +14343,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45740</v>
+        <v>46274</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14420,10 +14420,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45797</v>
+        <v>45280</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14479,7 +14479,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14493,10 +14493,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45797</v>
+        <v>45324</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14552,7 +14552,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14566,10 +14566,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45740</v>
+        <v>44593</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14625,7 +14625,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14639,10 +14639,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45804</v>
+        <v>45484</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14698,7 +14698,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14712,10 +14712,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45820</v>
+        <v>44964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14788,7 +14788,7 @@
         <v>45524</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45587</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45763</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE183"/>
+  <dimension ref="A1:AE182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,24 +1180,24 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50161-2021</t>
+          <t>S 2938-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44456</v>
+        <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>68.2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1239,134 +1239,21 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Jungfrulin
-Slåtterfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 50161-2021 artfynd.xlsx", "A 50161-2021")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 50161-2021 karta.png", "A 50161-2021")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 50161-2021 georefererad karta.tif", "A 50161-2021")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 50161-2021 FSC-klagomål.docx", "A 50161-2021")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 50161-2021 FSC-klagomål mail.docx", "A 50161-2021")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 50161-2021 tillsynsbegäran.docx", "A 50161-2021")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 50161-2021 tillsynsbegäran mail.docx", "A 50161-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S 2938-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45173</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Talltita
@@ -1374,43 +1261,150 @@
 Grönsiska</t>
         </is>
       </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/S 2938-2023 artfynd.xlsx", "S 2938-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/S 2938-2023 karta.png", "S 2938-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/S 2938-2023 georefererad karta.tif", "S 2938-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/S 2938-2023 FSC-klagomål.docx", "S 2938-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/S 2938-2023 FSC-klagomål mail.docx", "S 2938-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/S 2938-2023 tillsynsbegäran.docx", "S 2938-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/S 2938-2023 tillsynsbegäran mail.docx", "S 2938-2023")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/S 2938-2023 prioriterade fågelarter.docx", "S 2938-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 7821-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Slåtterfibbla
+Svinrot</t>
+        </is>
+      </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/S 2938-2023 artfynd.xlsx", "S 2938-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/S 2938-2023 karta.png", "S 2938-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/S 2938-2023 georefererad karta.tif", "S 2938-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/S 2938-2023 FSC-klagomål.docx", "S 2938-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/S 2938-2023 FSC-klagomål mail.docx", "S 2938-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/S 2938-2023 tillsynsbegäran.docx", "S 2938-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/S 2938-2023 tillsynsbegäran mail.docx", "S 2938-2023")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/S 2938-2023 prioriterade fågelarter.docx", "S 2938-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 45507-2024</t>
+          <t>A 35828-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1424,10 +1418,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45578</v>
+        <v>45532</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1440,19 +1434,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>6.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -1464,278 +1458,278 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37686-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 45507-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45578</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Knärot
 Lönnlav</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 7821-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>7</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Slåtterfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 35828-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45532</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Sommarfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 37686-2026</t>
+          <t>A 55897-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1749,10 +1743,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46279</v>
+        <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1765,84 +1759,87 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Sommarfibbla
-Svinrot</t>
+          <t>Spillkråka
+Kungsfågel</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55897-2021 artfynd.xlsx", "A 55897-2021")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55897-2021 karta.png", "A 55897-2021")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55897-2021 georefererad karta.tif", "A 55897-2021")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55897-2021 FSC-klagomål.docx", "A 55897-2021")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55897-2021 FSC-klagomål mail.docx", "A 55897-2021")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55897-2021 tillsynsbegäran.docx", "A 55897-2021")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55897-2021 tillsynsbegäran mail.docx", "A 55897-2021")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/A 55897-2021 prioriterade fågelarter.docx", "A 55897-2021")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55897-2021</t>
+          <t>A 7817-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1856,10 +1853,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44476</v>
+        <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1872,34 +1869,34 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>8.9</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -1908,51 +1905,47 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka
-Kungsfågel</t>
+          <t>Ask
+Huskvarnafibbla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55897-2021 artfynd.xlsx", "A 55897-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7817-2024 artfynd.xlsx", "A 7817-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55897-2021 karta.png", "A 55897-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7817-2024 karta.png", "A 7817-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55897-2021 georefererad karta.tif", "A 55897-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7817-2024 georefererad karta.tif", "A 7817-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55897-2021 FSC-klagomål.docx", "A 55897-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7817-2024 FSC-klagomål.docx", "A 7817-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55897-2021 FSC-klagomål mail.docx", "A 55897-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7817-2024 FSC-klagomål mail.docx", "A 7817-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55897-2021 tillsynsbegäran.docx", "A 55897-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7817-2024 tillsynsbegäran.docx", "A 7817-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55897-2021 tillsynsbegäran mail.docx", "A 55897-2021")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/A 55897-2021 prioriterade fågelarter.docx", "A 55897-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7817-2024 tillsynsbegäran mail.docx", "A 7817-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 7817-2024</t>
+          <t>A 7365-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1966,10 +1959,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45349</v>
+        <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,22 +1975,22 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.9</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2006,10 +1999,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2022,60 +2015,60 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Huskvarnafibbla</t>
+          <t>Fläcknycklar
+Grönvit nattviol</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7817-2024 artfynd.xlsx", "A 7817-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7365-2023 artfynd.xlsx", "A 7365-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7817-2024 karta.png", "A 7817-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7365-2023 karta.png", "A 7365-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7817-2024 georefererad karta.tif", "A 7817-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7365-2023 georefererad karta.tif", "A 7365-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7817-2024 FSC-klagomål.docx", "A 7817-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7365-2023 FSC-klagomål.docx", "A 7365-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7817-2024 FSC-klagomål mail.docx", "A 7817-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7365-2023 FSC-klagomål mail.docx", "A 7365-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7817-2024 tillsynsbegäran.docx", "A 7817-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7365-2023 tillsynsbegäran.docx", "A 7365-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7817-2024 tillsynsbegäran mail.docx", "A 7817-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7365-2023 tillsynsbegäran mail.docx", "A 7365-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 7365-2023</t>
+          <t>S 3854-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44971</v>
+        <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2088,7 +2081,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>45.6</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
@@ -2103,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2112,10 +2105,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2124,64 +2117,68 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar
-Grönvit nattviol</t>
+          <t>Pärluggla
+Orre</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7365-2023 artfynd.xlsx", "A 7365-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/S 3854-2022 artfynd.xlsx", "S 3854-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7365-2023 karta.png", "A 7365-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/S 3854-2022 karta.png", "S 3854-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7365-2023 georefererad karta.tif", "A 7365-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/S 3854-2022 georefererad karta.tif", "S 3854-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7365-2023 FSC-klagomål.docx", "A 7365-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/S 3854-2022 FSC-klagomål.docx", "S 3854-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7365-2023 FSC-klagomål mail.docx", "A 7365-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/S 3854-2022 FSC-klagomål mail.docx", "S 3854-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7365-2023 tillsynsbegäran.docx", "A 7365-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/S 3854-2022 tillsynsbegäran.docx", "S 3854-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7365-2023 tillsynsbegäran mail.docx", "A 7365-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/S 3854-2022 tillsynsbegäran mail.docx", "S 3854-2022")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/S 3854-2022 prioriterade fågelarter.docx", "S 3854-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S 3854-2022</t>
+          <t>A 47692-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44747</v>
+        <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,10 +2191,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>45.6</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2209,72 +2206,71 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Pärluggla
-Orre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/S 3854-2022 artfynd.xlsx", "S 3854-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 47692-2022 artfynd.xlsx", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/S 3854-2022 karta.png", "S 3854-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 47692-2022 karta.png", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/S 3854-2022 georefererad karta.tif", "S 3854-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 47692-2022 georefererad karta.tif", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/S 3854-2022 FSC-klagomål.docx", "S 3854-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 47692-2022 FSC-klagomål.docx", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/S 3854-2022 FSC-klagomål mail.docx", "S 3854-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 47692-2022 FSC-klagomål mail.docx", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/S 3854-2022 tillsynsbegäran.docx", "S 3854-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 47692-2022 tillsynsbegäran.docx", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/S 3854-2022 tillsynsbegäran mail.docx", "S 3854-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 47692-2022 tillsynsbegäran mail.docx", "A 47692-2022")</f>
         <v/>
       </c>
       <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/S 3854-2022 prioriterade fågelarter.docx", "S 3854-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/A 47692-2022 prioriterade fågelarter.docx", "A 47692-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 47692-2022</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2288,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44854</v>
+        <v>44846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2304,20 +2300,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2328,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2340,50 +2336,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 47692-2022 artfynd.xlsx", "A 47692-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 47692-2022 karta.png", "A 47692-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 47692-2022 georefererad karta.tif", "A 47692-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 47692-2022 FSC-klagomål.docx", "A 47692-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 47692-2022 FSC-klagomål mail.docx", "A 47692-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 47692-2022 tillsynsbegäran.docx", "A 47692-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 47692-2022 tillsynsbegäran mail.docx", "A 47692-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/A 47692-2022 prioriterade fågelarter.docx", "A 47692-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2397,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45393</v>
+        <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2413,17 +2405,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2437,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2453,42 +2445,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 62232-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2502,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46031</v>
+        <v>44922</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2517,13 +2509,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2532,13 +2519,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2550,55 +2537,55 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2612,10 +2599,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44890</v>
+        <v>45401</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2620,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2645,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2657,10 +2644,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2673,42 +2660,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2718,14 +2709,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45401</v>
+        <v>46122</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2737,13 +2728,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2755,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2767,62 +2753,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2832,14 +2814,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45972</v>
+        <v>45393</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2852,13 +2834,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2867,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2876,58 +2858,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2937,14 +2919,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45349</v>
+        <v>45629</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,8 +2938,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2997,42 +2984,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3042,14 +3029,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46122</v>
+        <v>45007</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3062,13 +3049,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3095,49 +3082,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3147,14 +3134,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44846</v>
+        <v>45972</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3167,7 +3154,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3179,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3200,49 +3187,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62232-2022</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3256,10 +3243,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44922</v>
+        <v>44890</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,11 +3258,16 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3287,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3296,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3308,46 +3300,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3361,10 +3353,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45629</v>
+        <v>46031</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3382,7 +3374,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3415,49 +3407,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3471,10 +3463,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45007</v>
+        <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3486,21 +3478,26 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3511,10 +3508,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3527,59 +3524,59 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>S 694-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45189</v>
+        <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3591,16 +3588,11 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>59.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3609,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3621,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3633,63 +3625,67 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/S 694-2026 artfynd.xlsx", "S 694-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/S 694-2026 karta.png", "S 694-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/S 694-2026 georefererad karta.tif", "S 694-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/S 694-2026 FSC-klagomål.docx", "S 694-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/S 694-2026 FSC-klagomål mail.docx", "S 694-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/S 694-2026 tillsynsbegäran.docx", "S 694-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/S 694-2026 tillsynsbegäran mail.docx", "S 694-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/S 694-2026 prioriterade fågelarter.docx", "S 694-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S 694-2026</t>
+          <t>A 55888-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46091</v>
+        <v>44476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3702,10 +3698,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>59.7</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3732,56 +3728,20 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/S 694-2026 artfynd.xlsx", "S 694-2026")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/S 694-2026 karta.png", "S 694-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/S 694-2026 georefererad karta.tif", "S 694-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/S 694-2026 FSC-klagomål.docx", "S 694-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/S 694-2026 FSC-klagomål mail.docx", "S 694-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/S 694-2026 tillsynsbegäran.docx", "S 694-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/S 694-2026 tillsynsbegäran mail.docx", "S 694-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/fåglar/S 694-2026 prioriterade fågelarter.docx", "S 694-2026")</f>
-        <v/>
-      </c>
+      <c r="V30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55888-2021</t>
+          <t>A 65493-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3795,10 +3755,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44476</v>
+        <v>44516</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3810,8 +3770,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3854,7 +3819,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 65493-2021</t>
+          <t>A 39354-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3868,10 +3833,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44516</v>
+        <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3883,13 +3848,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3932,7 +3892,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 39354-2022</t>
+          <t>A 52062-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3942,14 +3902,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44817</v>
+        <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3962,7 +3922,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4005,7 +3965,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52062-2022</t>
+          <t>A 52058-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4022,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4035,7 +3995,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4078,7 +4038,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 52058-2022</t>
+          <t>A 55896-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4088,14 +4048,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44873</v>
+        <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4108,7 +4068,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4151,7 +4111,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 55896-2021</t>
+          <t>A 57229-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4165,10 +4125,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44476</v>
+        <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4181,7 +4141,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4224,7 +4184,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57229-2021</t>
+          <t>A 9903-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4238,10 +4198,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44483</v>
+        <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4254,7 +4214,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>16.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4297,7 +4257,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9903-2022</t>
+          <t>A 13811-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4311,10 +4271,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44620</v>
+        <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4327,7 +4287,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>16.8</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4370,7 +4330,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13811-2022</t>
+          <t>A 62452-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4384,10 +4344,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44649</v>
+        <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4400,7 +4360,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4443,7 +4403,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62452-2021</t>
+          <t>A 27760-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4457,10 +4417,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44503</v>
+        <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4473,7 +4433,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4516,7 +4476,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27760-2022</t>
+          <t>A 21691-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4530,10 +4490,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44743</v>
+        <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4546,7 +4506,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4589,7 +4549,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21691-2022</t>
+          <t>A 16133-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4603,10 +4563,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44707</v>
+        <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4619,7 +4579,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4662,7 +4622,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16133-2022</t>
+          <t>A 21693-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4676,10 +4636,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44665</v>
+        <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4692,7 +4652,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4735,7 +4695,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21693-2022</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4749,10 +4709,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44707</v>
+        <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4765,7 +4725,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4808,7 +4768,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4822,10 +4782,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45145</v>
+        <v>45702</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4838,7 +4798,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4881,7 +4841,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4895,10 +4855,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45682</v>
+        <v>44817</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4911,7 +4871,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4954,7 +4914,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4964,14 +4924,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44707</v>
+        <v>44832</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5027,7 +4987,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5041,10 +5001,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45543</v>
+        <v>45455</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5057,7 +5017,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5100,7 +5060,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5114,10 +5074,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45543</v>
+        <v>44895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5130,7 +5090,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5173,7 +5133,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5183,14 +5143,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45478</v>
+        <v>44964</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5203,7 +5163,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5246,7 +5206,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5260,10 +5220,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44538</v>
+        <v>44964</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5276,7 +5236,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5319,7 +5279,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5336,7 +5296,7 @@
         <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5349,7 +5309,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5392,7 +5352,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5406,10 +5366,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44964</v>
+        <v>44869</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5422,7 +5382,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>10.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5465,7 +5425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5479,10 +5439,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45596</v>
+        <v>45469</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5495,7 +5455,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5538,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33875-2024</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5552,10 +5512,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45521</v>
+        <v>45529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5568,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5611,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5625,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45797</v>
+        <v>45553</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5641,7 +5601,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5684,7 +5644,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5698,10 +5658,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45638</v>
+        <v>44889</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5714,7 +5674,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>14.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5757,7 +5717,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5771,10 +5731,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45553</v>
+        <v>44964</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5787,7 +5747,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5830,7 +5790,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5844,10 +5804,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45740</v>
+        <v>45321</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5860,7 +5820,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5903,7 +5863,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 33875-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5917,10 +5877,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45797</v>
+        <v>45521</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5933,7 +5893,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5976,7 +5936,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5990,10 +5950,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45740</v>
+        <v>44896</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6006,7 +5966,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6049,7 +6009,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6059,14 +6019,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44966</v>
+        <v>45393</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6079,7 +6039,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6122,7 +6082,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6136,10 +6096,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45804</v>
+        <v>45820</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6152,7 +6112,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6195,7 +6155,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6209,10 +6169,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46031</v>
+        <v>44670</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6225,7 +6185,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6268,7 +6228,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6282,10 +6242,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45169</v>
+        <v>45553</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6298,7 +6258,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6341,7 +6301,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6355,10 +6315,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45529</v>
+        <v>44656</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6371,7 +6331,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6414,7 +6374,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6428,10 +6388,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45890</v>
+        <v>44707</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6444,7 +6404,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6487,7 +6447,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6501,10 +6461,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45820</v>
+        <v>45596</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6517,7 +6477,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.7</v>
+        <v>15.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6560,7 +6520,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6570,14 +6530,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45686</v>
+        <v>46088</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6590,7 +6550,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6633,7 +6593,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6647,10 +6607,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45904</v>
+        <v>45251</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6662,13 +6622,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6711,7 +6666,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6721,14 +6676,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45495</v>
+        <v>44998</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6741,7 +6696,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6784,7 +6739,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43134-2025</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6798,10 +6753,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45909</v>
+        <v>45890</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6814,7 +6769,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6857,7 +6812,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6871,10 +6826,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44742</v>
+        <v>45638</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6887,7 +6842,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6930,7 +6885,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6944,10 +6899,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45702</v>
+        <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6960,7 +6915,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7003,7 +6958,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7017,10 +6972,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45926</v>
+        <v>45875</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7033,7 +6988,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7076,7 +7031,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7090,10 +7045,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45926</v>
+        <v>45875</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7106,7 +7061,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7149,7 +7104,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46533-2025</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7163,10 +7118,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45926</v>
+        <v>45877</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7222,7 +7177,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7236,10 +7191,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45928</v>
+        <v>45877</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7252,7 +7207,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7295,7 +7250,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7305,14 +7260,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45933</v>
+        <v>46126</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7325,7 +7280,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7368,7 +7323,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7382,10 +7337,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45048</v>
+        <v>45204</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7398,7 +7353,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7441,7 +7396,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7455,10 +7410,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45875</v>
+        <v>45596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7471,7 +7426,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7514,7 +7469,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7528,10 +7483,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45940</v>
+        <v>45904</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7543,8 +7498,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7587,7 +7547,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 43134-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7601,10 +7561,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45875</v>
+        <v>45909</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7617,7 +7577,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7660,7 +7620,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7674,10 +7634,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44964</v>
+        <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7690,7 +7650,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7733,7 +7693,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7747,10 +7707,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45877</v>
+        <v>45820</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7763,7 +7723,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>7.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7806,7 +7766,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 46533-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7820,10 +7780,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45877</v>
+        <v>45926</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7836,7 +7796,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7879,7 +7839,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7889,14 +7849,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44964</v>
+        <v>45752</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7909,7 +7869,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>9.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7952,7 +7912,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7966,10 +7926,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45953</v>
+        <v>45169</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7982,7 +7942,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8025,7 +7985,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8039,10 +7999,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45596</v>
+        <v>45246</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8055,7 +8015,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>15.1</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8098,7 +8058,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8112,10 +8072,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45553</v>
+        <v>45730</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8128,7 +8088,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8171,7 +8131,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8181,14 +8141,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45393</v>
+        <v>45926</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8201,7 +8161,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8244,7 +8204,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8258,10 +8218,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44896</v>
+        <v>45016</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8274,7 +8234,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8317,7 +8277,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8331,10 +8291,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45676</v>
+        <v>45926</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8347,7 +8307,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8390,7 +8350,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8404,10 +8364,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44700</v>
+        <v>44865</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8420,7 +8380,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8463,7 +8423,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8473,14 +8433,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46088</v>
+        <v>45928</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8493,7 +8453,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8536,7 +8496,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8550,10 +8510,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45446</v>
+        <v>45083</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8566,7 +8526,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>13.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8609,7 +8569,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8619,14 +8579,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46007</v>
+        <v>45752</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8639,7 +8599,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8682,7 +8642,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8696,10 +8656,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46009</v>
+        <v>45752</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8712,7 +8672,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8755,7 +8715,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8769,10 +8729,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44964</v>
+        <v>45752</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8785,7 +8745,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8828,7 +8788,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8842,10 +8802,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44964</v>
+        <v>45495</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8858,7 +8818,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8901,7 +8861,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8915,10 +8875,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45214</v>
+        <v>45933</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8931,7 +8891,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8974,7 +8934,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8988,10 +8948,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45748</v>
+        <v>45313</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9004,7 +8964,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9047,7 +9007,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9061,10 +9021,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45103</v>
+        <v>44954</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9077,7 +9037,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9120,7 +9080,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9134,10 +9094,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45145</v>
+        <v>44992</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9150,7 +9110,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9193,7 +9153,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9207,10 +9167,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45755</v>
+        <v>45940</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9223,7 +9183,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9266,7 +9226,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9280,10 +9240,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45755</v>
+        <v>44938</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9296,7 +9256,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9339,7 +9299,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9353,10 +9313,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45752</v>
+        <v>45145</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9369,7 +9329,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9412,7 +9372,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 1489-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9426,10 +9386,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45752</v>
+        <v>45305</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9442,7 +9402,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9485,7 +9445,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9499,10 +9459,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45752</v>
+        <v>45048</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9515,7 +9475,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9558,7 +9518,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9572,10 +9532,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45201</v>
+        <v>45401</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9588,7 +9548,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9631,7 +9591,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9641,14 +9601,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46126</v>
+        <v>45953</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9661,7 +9621,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9704,7 +9664,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9718,10 +9678,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45169</v>
+        <v>45543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9734,7 +9694,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9777,7 +9737,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9791,10 +9751,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44977</v>
+        <v>45543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9807,7 +9767,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9850,7 +9810,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9860,14 +9820,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
         <v>45752</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9880,7 +9840,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>9.6</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9923,7 +9883,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9937,10 +9897,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44607</v>
+        <v>45145</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9953,7 +9913,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9996,7 +9956,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10010,10 +9970,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44670</v>
+        <v>46197</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10069,7 +10029,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10083,10 +10043,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45313</v>
+        <v>46197</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10099,7 +10059,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10142,7 +10102,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10156,10 +10116,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45637</v>
+        <v>45201</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10172,7 +10132,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10215,7 +10175,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10229,10 +10189,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45820</v>
+        <v>45170</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10245,7 +10205,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10288,7 +10248,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10302,10 +10262,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45730</v>
+        <v>45371</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10318,7 +10278,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10361,7 +10321,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10375,10 +10335,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45455</v>
+        <v>45682</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10391,7 +10351,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10434,7 +10394,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10448,10 +10408,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45083</v>
+        <v>45169</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10464,7 +10424,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>13.1</v>
+        <v>4.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10507,7 +10467,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10521,10 +10481,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45372</v>
+        <v>45686</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10536,13 +10496,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10585,7 +10540,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10599,10 +10554,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45740</v>
+        <v>44656</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10615,7 +10570,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10658,7 +10613,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10672,10 +10627,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44970</v>
+        <v>44656</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10687,13 +10642,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10732,31 +10682,11 @@
         <v>0</v>
       </c>
       <c r="V125" s="2" t="inlineStr"/>
-      <c r="Z125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10770,10 +10700,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44954</v>
+        <v>45214</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10786,7 +10716,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10829,7 +10759,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10843,10 +10773,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45313</v>
+        <v>45637</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10859,7 +10789,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10902,7 +10832,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10916,10 +10846,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44656</v>
+        <v>46246</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10932,7 +10862,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10975,7 +10905,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10989,10 +10919,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44817</v>
+        <v>46246</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11005,7 +10935,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11048,7 +10978,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11062,10 +10992,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44895</v>
+        <v>44670</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11078,7 +11008,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11121,7 +11051,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11135,10 +11065,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45455</v>
+        <v>45740</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11151,7 +11081,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11194,7 +11124,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1489-2024</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11208,10 +11138,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45305</v>
+        <v>44796</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11224,7 +11154,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11267,7 +11197,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11281,10 +11211,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44869</v>
+        <v>46216</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11297,7 +11227,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>10.9</v>
+        <v>3.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11340,7 +11270,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11354,10 +11284,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44889</v>
+        <v>46216</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11370,7 +11300,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>14.1</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11413,7 +11343,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11427,10 +11357,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44954</v>
+        <v>45372</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11442,8 +11372,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11486,7 +11421,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11500,10 +11435,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44954</v>
+        <v>46260</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11516,7 +11451,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11559,7 +11494,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11569,14 +11504,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44998</v>
+        <v>45313</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11589,7 +11524,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11632,7 +11567,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11646,10 +11581,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44865</v>
+        <v>46268</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11662,7 +11597,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11705,7 +11640,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11719,10 +11654,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44993</v>
+        <v>46268</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11735,7 +11670,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11778,7 +11713,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11788,14 +11723,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45244</v>
+        <v>46007</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11808,7 +11743,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11851,7 +11786,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11865,10 +11800,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45702</v>
+        <v>46268</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11881,7 +11816,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11924,7 +11859,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11938,10 +11873,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46197</v>
+        <v>44966</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11954,7 +11889,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11997,7 +11932,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12007,14 +11942,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44938</v>
+        <v>45478</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12027,7 +11962,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12070,7 +12005,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12084,10 +12019,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44796</v>
+        <v>46009</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12100,7 +12035,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12143,7 +12078,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12157,10 +12092,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46240</v>
+        <v>45748</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12173,7 +12108,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12216,7 +12151,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12230,10 +12165,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46197</v>
+        <v>46232</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12246,7 +12181,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12289,7 +12224,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12303,10 +12238,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44656</v>
+        <v>45371</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12319,7 +12254,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12362,7 +12297,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12376,10 +12311,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44656</v>
+        <v>44954</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12392,7 +12327,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12435,7 +12370,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12449,10 +12384,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46246</v>
+        <v>44993</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12465,7 +12400,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12508,7 +12443,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12522,10 +12457,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45469</v>
+        <v>44964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12538,7 +12473,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12581,7 +12516,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12595,10 +12530,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46246</v>
+        <v>45450</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12611,7 +12546,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12654,7 +12589,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12668,10 +12603,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44832</v>
+        <v>46274</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12684,7 +12619,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12727,7 +12662,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12741,10 +12676,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45321</v>
+        <v>44970</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12756,8 +12691,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12796,11 +12736,31 @@
         <v>0</v>
       </c>
       <c r="V153" s="2" t="inlineStr"/>
+      <c r="Z153">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA153">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB153">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC153">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD153">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12814,10 +12774,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45170</v>
+        <v>45103</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12830,7 +12790,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12873,7 +12833,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12887,10 +12847,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46216</v>
+        <v>44538</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12903,7 +12863,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12946,7 +12906,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12960,10 +12920,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46216</v>
+        <v>46031</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12976,7 +12936,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13019,7 +12979,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13033,10 +12993,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45401</v>
+        <v>46240</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13049,7 +13009,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13092,7 +13052,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13106,10 +13066,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44992</v>
+        <v>46240</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13122,7 +13082,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13165,7 +13125,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13175,14 +13135,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46260</v>
+        <v>45244</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13195,7 +13155,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13238,7 +13198,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13252,10 +13212,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45371</v>
+        <v>45455</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13268,7 +13228,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13311,7 +13271,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13325,10 +13285,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46240</v>
+        <v>44954</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13341,7 +13301,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13384,7 +13344,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13398,10 +13358,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44952</v>
+        <v>44964</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13414,7 +13374,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13457,7 +13417,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13471,10 +13431,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45204</v>
+        <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13487,7 +13447,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13530,7 +13490,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13544,10 +13504,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45450</v>
+        <v>45755</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13560,7 +13520,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13603,7 +13563,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13617,10 +13577,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46268</v>
+        <v>45446</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13633,7 +13593,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13676,7 +13636,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13690,10 +13650,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46268</v>
+        <v>45676</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13706,7 +13666,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13749,7 +13709,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13763,10 +13723,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45016</v>
+        <v>44742</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13779,7 +13739,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13822,7 +13782,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13836,10 +13796,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46268</v>
+        <v>44700</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13852,7 +13812,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13895,7 +13855,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13909,10 +13869,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45752</v>
+        <v>44952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13925,7 +13885,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13968,7 +13928,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13982,10 +13942,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45251</v>
+        <v>45280</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13998,7 +13958,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14041,7 +14001,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14055,10 +14015,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44670</v>
+        <v>45324</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14071,7 +14031,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14114,7 +14074,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14128,10 +14088,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45371</v>
+        <v>44593</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14144,7 +14104,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14187,7 +14147,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14201,10 +14161,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46232</v>
+        <v>45484</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14217,7 +14177,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14260,7 +14220,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14274,10 +14234,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45246</v>
+        <v>44964</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14290,7 +14250,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14333,7 +14293,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14343,14 +14303,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46274</v>
+        <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14363,7 +14323,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14406,7 +14366,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14420,10 +14380,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45280</v>
+        <v>45797</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14436,7 +14396,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14479,7 +14439,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14493,10 +14453,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45324</v>
+        <v>45797</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14509,7 +14469,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14552,7 +14512,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14566,10 +14526,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44593</v>
+        <v>45740</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14582,7 +14542,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14625,7 +14585,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14639,10 +14599,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45484</v>
+        <v>45804</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14655,7 +14615,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14698,24 +14658,24 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>S 3179-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44964</v>
+        <v>45524</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14728,7 +14688,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14771,7 +14731,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S 3179-2024</t>
+          <t>S 4371-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14785,10 +14745,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45524</v>
+        <v>45587</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14801,7 +14761,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14841,10 +14801,10 @@
       </c>
       <c r="V181" s="2" t="inlineStr"/>
     </row>
-    <row r="182" ht="15" customHeight="1">
+    <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S 4371-2024</t>
+          <t>S 1255-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14854,14 +14814,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45587</v>
+        <v>45763</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14874,7 +14834,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.5</v>
+        <v>35.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14913,79 +14873,6 @@
         <v>0</v>
       </c>
       <c r="V182" s="2" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>S 1255-2025</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D183" s="1" t="n">
-        <v>45763</v>
-      </c>
-      <c r="E183" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I183" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="J183" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" t="n">
-        <v>0</v>
-      </c>
-      <c r="M183" t="n">
-        <v>0</v>
-      </c>
-      <c r="N183" t="n">
-        <v>0</v>
-      </c>
-      <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="n">
-        <v>0</v>
-      </c>
-      <c r="T183" t="n">
-        <v>0</v>
-      </c>
-      <c r="U183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V183" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7821-2024</t>
+          <t>A 45507-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45349</v>
+        <v>45578</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1327,22 +1327,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1351,378 +1351,378 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Knärot
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7821-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>9</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Slåtterfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 35828-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45532</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>6.7</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 37686-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>5.1</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 45507-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45578</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Knärot
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44846</v>
+        <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,19 +2300,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2336,39 +2336,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 62232-2022</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44922</v>
+        <v>44846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2522,10 +2522,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2546,46 +2546,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,14 +2595,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45401</v>
+        <v>45972</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2614,28 +2614,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2653,53 +2648,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,14 +2700,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46122</v>
+        <v>46031</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2728,18 +2719,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2753,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2762,49 +2758,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2814,14 +2810,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45393</v>
+        <v>44890</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,14 +2829,19 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2870,46 +2871,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 62232-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2923,10 +2924,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45629</v>
+        <v>44922</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2938,13 +2939,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2953,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2971,7 +2967,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2984,42 +2980,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3033,10 +3029,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45007</v>
+        <v>45629</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3048,18 +3044,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3073,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3085,46 +3086,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,14 +3135,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45972</v>
+        <v>46122</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3154,10 +3155,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3169,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3178,58 +3179,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3243,10 +3244,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44890</v>
+        <v>45007</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3258,19 +3259,14 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3304,42 +3300,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3353,10 +3349,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46031</v>
+        <v>45189</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3374,7 +3370,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3383,10 +3379,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3401,55 +3397,55 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
         <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3463,10 +3459,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45189</v>
+        <v>45401</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3480,14 +3476,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3524,35 +3520,39 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>44516</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45702</v>
+        <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45702</v>
+        <v>45682</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44817</v>
+        <v>45543</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44832</v>
+        <v>45543</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45455</v>
+        <v>44707</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5060,7 +5060,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44895</v>
+        <v>45478</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44964</v>
+        <v>44538</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5223,7 +5223,7 @@
         <v>44964</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5296,7 +5296,7 @@
         <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5352,7 +5352,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44869</v>
+        <v>45596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10.9</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 33875-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45469</v>
+        <v>45521</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45529</v>
+        <v>45553</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>6.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45553</v>
+        <v>45638</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44889</v>
+        <v>44966</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>14.1</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44964</v>
+        <v>45169</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45321</v>
+        <v>45686</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33875-2024</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45521</v>
+        <v>45495</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44896</v>
+        <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6019,14 +6019,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45393</v>
+        <v>45529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45820</v>
+        <v>45702</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44670</v>
+        <v>45048</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45553</v>
+        <v>44964</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6301,7 +6301,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44656</v>
+        <v>44964</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6374,7 +6374,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44707</v>
+        <v>45553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6464,7 +6464,7 @@
         <v>45596</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46088</v>
+        <v>45393</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6593,7 +6593,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45251</v>
+        <v>44896</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6676,14 +6676,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44998</v>
+        <v>45676</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6739,7 +6739,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45890</v>
+        <v>44700</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45638</v>
+        <v>45890</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44977</v>
+        <v>45820</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.7</v>
+        <v>7.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6958,7 +6958,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45875</v>
+        <v>45730</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7031,7 +7031,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45875</v>
+        <v>45904</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7060,8 +7060,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7104,7 +7109,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7118,10 +7123,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45877</v>
+        <v>45446</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7134,7 +7139,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7177,7 +7182,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7191,10 +7196,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45877</v>
+        <v>44964</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7207,7 +7212,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7250,7 +7255,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7260,14 +7265,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46126</v>
+        <v>44964</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7280,7 +7285,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7323,7 +7328,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 43134-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7337,10 +7342,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45204</v>
+        <v>45909</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7353,7 +7358,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7396,7 +7401,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7410,10 +7415,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45596</v>
+        <v>45214</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7426,7 +7431,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7469,7 +7474,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7483,10 +7488,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45904</v>
+        <v>45083</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7498,13 +7503,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>13.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43134-2025</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45909</v>
+        <v>45103</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44607</v>
+        <v>45926</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45820</v>
+        <v>45926</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
         <v>45926</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45752</v>
+        <v>45928</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>9.6</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45169</v>
+        <v>45145</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7999,10 +7999,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45246</v>
+        <v>45933</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8058,7 +8058,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45730</v>
+        <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8131,7 +8131,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45926</v>
+        <v>45755</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45016</v>
+        <v>45752</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45926</v>
+        <v>45752</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44865</v>
+        <v>45752</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45928</v>
+        <v>45201</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8496,7 +8496,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45083</v>
+        <v>45940</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>13.1</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45752</v>
+        <v>45169</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45752</v>
+        <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45752</v>
+        <v>45953</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8788,7 +8788,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8798,14 +8798,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45495</v>
+        <v>45752</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>9.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45933</v>
+        <v>44670</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>45313</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44954</v>
+        <v>45637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44992</v>
+        <v>45455</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45940</v>
+        <v>45372</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9182,8 +9182,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9226,7 +9231,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9236,14 +9241,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44938</v>
+        <v>46007</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9256,7 +9261,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9299,7 +9304,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9313,10 +9318,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45145</v>
+        <v>46009</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9329,7 +9334,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9372,7 +9377,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1489-2024</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9386,10 +9391,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45305</v>
+        <v>45740</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9402,7 +9407,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9445,7 +9450,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9459,10 +9464,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45048</v>
+        <v>44970</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9474,8 +9479,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9514,11 +9524,31 @@
         <v>0</v>
       </c>
       <c r="V109" s="2" t="inlineStr"/>
+      <c r="Z109">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA109">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB109">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC109">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD109">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9532,10 +9562,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45401</v>
+        <v>45748</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9548,7 +9578,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9591,7 +9621,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9605,10 +9635,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45953</v>
+        <v>44954</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9621,7 +9651,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9664,7 +9694,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9678,10 +9708,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45543</v>
+        <v>46031</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9694,7 +9724,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9737,7 +9767,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9751,10 +9781,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45543</v>
+        <v>45313</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9767,7 +9797,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9810,7 +9840,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9824,10 +9854,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45752</v>
+        <v>44656</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9840,7 +9870,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9883,7 +9913,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9897,10 +9927,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45145</v>
+        <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9913,7 +9943,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9956,7 +9986,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9970,10 +10000,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46197</v>
+        <v>44895</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9986,7 +10016,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10029,7 +10059,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10043,10 +10073,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46197</v>
+        <v>45455</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10059,7 +10089,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10102,7 +10132,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 1489-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10116,10 +10146,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45201</v>
+        <v>45305</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10132,7 +10162,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10175,7 +10205,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10189,10 +10219,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45170</v>
+        <v>44869</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10205,7 +10235,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>10.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10248,7 +10278,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10262,10 +10292,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45371</v>
+        <v>44889</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10278,7 +10308,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>14.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10321,7 +10351,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10335,10 +10365,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45682</v>
+        <v>44954</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10351,7 +10381,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10394,7 +10424,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10408,10 +10438,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45169</v>
+        <v>44954</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10424,7 +10454,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10467,7 +10497,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10477,14 +10507,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45686</v>
+        <v>44998</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10497,7 +10527,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10540,7 +10570,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10554,10 +10584,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44656</v>
+        <v>44865</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10570,7 +10600,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10613,7 +10643,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10623,14 +10653,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44656</v>
+        <v>46088</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10643,7 +10673,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10686,7 +10716,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10700,10 +10730,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45214</v>
+        <v>44993</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10716,7 +10746,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10759,7 +10789,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10769,14 +10799,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45637</v>
+        <v>45244</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10789,7 +10819,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10832,7 +10862,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10846,10 +10876,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46246</v>
+        <v>45702</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10862,7 +10892,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10905,7 +10935,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10919,10 +10949,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46246</v>
+        <v>46197</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10935,7 +10965,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10978,7 +11008,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10992,10 +11022,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44670</v>
+        <v>46197</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11051,7 +11081,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11065,10 +11095,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45740</v>
+        <v>44938</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11081,7 +11111,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11141,7 +11171,7 @@
         <v>44796</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11197,7 +11227,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11211,10 +11241,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46216</v>
+        <v>44656</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11227,7 +11257,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11270,7 +11300,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11284,10 +11314,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46216</v>
+        <v>44656</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11300,7 +11330,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11343,7 +11373,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11353,14 +11383,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45372</v>
+        <v>46126</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11372,13 +11402,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11421,7 +11446,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11435,10 +11460,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46260</v>
+        <v>45469</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11451,7 +11476,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11494,7 +11519,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11508,10 +11533,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45313</v>
+        <v>46246</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11524,7 +11549,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11567,7 +11592,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11577,14 +11602,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46268</v>
+        <v>44832</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11597,7 +11622,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11640,7 +11665,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11654,10 +11679,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46268</v>
+        <v>44607</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11670,7 +11695,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11713,7 +11738,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11723,14 +11748,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46007</v>
+        <v>45321</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11786,7 +11811,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11800,10 +11825,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46268</v>
+        <v>45170</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11816,7 +11841,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11859,7 +11884,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11873,10 +11898,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44966</v>
+        <v>46246</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11889,7 +11914,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11932,7 +11957,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11942,14 +11967,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45478</v>
+        <v>45401</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11962,7 +11987,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12005,7 +12030,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12019,10 +12044,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46009</v>
+        <v>44992</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12035,7 +12060,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12078,7 +12103,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12092,10 +12117,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45748</v>
+        <v>45371</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12108,7 +12133,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12151,7 +12176,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12165,10 +12190,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46232</v>
+        <v>44952</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12181,7 +12206,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12224,7 +12249,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12238,10 +12263,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45371</v>
+        <v>45204</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12254,7 +12279,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12297,7 +12322,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12311,10 +12336,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44954</v>
+        <v>45450</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12327,7 +12352,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12370,7 +12395,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12384,10 +12409,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44993</v>
+        <v>46216</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12400,7 +12425,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12443,7 +12468,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12457,10 +12482,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44964</v>
+        <v>46216</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12473,7 +12498,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12516,7 +12541,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12530,10 +12555,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45450</v>
+        <v>45016</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12546,7 +12571,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12589,7 +12614,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12599,14 +12624,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46274</v>
+        <v>45752</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12619,7 +12644,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12662,7 +12687,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12676,10 +12701,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44970</v>
+        <v>46260</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12691,13 +12716,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12736,31 +12756,11 @@
         <v>0</v>
       </c>
       <c r="V153" s="2" t="inlineStr"/>
-      <c r="Z153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45103</v>
+        <v>45251</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12833,7 +12833,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44538</v>
+        <v>44670</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12906,7 +12906,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46031</v>
+        <v>45371</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46240</v>
+        <v>45246</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>8</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13052,7 +13052,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13066,10 +13066,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46240</v>
+        <v>46268</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13125,7 +13125,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13135,14 +13135,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45244</v>
+        <v>46268</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45455</v>
+        <v>46268</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13271,7 +13271,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44954</v>
+        <v>45280</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13344,7 +13344,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44964</v>
+        <v>45324</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45755</v>
+        <v>46232</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13490,7 +13490,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13504,10 +13504,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45755</v>
+        <v>44593</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13563,7 +13563,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13573,14 +13573,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45446</v>
+        <v>46274</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13636,7 +13636,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45676</v>
+        <v>45484</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44742</v>
+        <v>44964</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13782,7 +13782,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44700</v>
+        <v>45797</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13855,7 +13855,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13869,10 +13869,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44952</v>
+        <v>46240</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45280</v>
+        <v>45740</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14001,7 +14001,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14015,10 +14015,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45324</v>
+        <v>46240</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14074,7 +14074,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44593</v>
+        <v>45797</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14147,7 +14147,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14161,10 +14161,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45484</v>
+        <v>45740</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44964</v>
+        <v>45804</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14307,10 +14307,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45740</v>
+        <v>45820</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45797</v>
+        <v>45875</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14439,7 +14439,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14453,10 +14453,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45797</v>
+        <v>45875</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14512,7 +14512,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14526,10 +14526,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45740</v>
+        <v>45877</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14585,7 +14585,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14599,10 +14599,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45804</v>
+        <v>45877</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>45524</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45587</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45763</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45578</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45349</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45532</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>46279</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45972</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>46031</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44890</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44922</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45629</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>46122</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45007</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45189</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>45401</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>44516</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>45682</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>45543</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45543</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>44707</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45478</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44538</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44964</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45521</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45553</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>45638</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>44966</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45169</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>45686</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>45495</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>45529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45702</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45048</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44964</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>44964</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45596</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45393</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>44896</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>45676</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44700</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45890</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45820</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45730</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45904</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45446</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>44964</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>44964</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45909</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45214</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>45083</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>45103</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>45926</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>45926</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45926</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>45928</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45145</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>45933</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45755</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>45752</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>45752</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>45752</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45201</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45940</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>45169</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45953</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45752</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44670</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45313</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45455</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45372</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>46007</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>46009</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>45740</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>44970</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>45748</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>44954</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>46031</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45313</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44656</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44895</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45455</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45305</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44869</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44889</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>44954</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>44954</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44998</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44865</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>46088</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>44993</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>45244</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>45702</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>46197</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>46197</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44938</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44796</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44656</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44656</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>46126</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45469</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>46246</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44832</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>44607</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45321</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45170</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>46246</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45401</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>44992</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45371</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>44952</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45204</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>45450</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>46216</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>46216</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>45016</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45752</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>46260</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45251</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>44670</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45371</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45246</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>46268</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>46268</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>46268</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45280</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45324</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>46232</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44593</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>46274</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45484</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44964</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45797</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>46240</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45740</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>46240</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45797</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45740</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45804</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45820</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>45875</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45875</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45877</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45877</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45524</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45587</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45763</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE182"/>
+  <dimension ref="A1:AE181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45578</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45349</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35828-2024</t>
+          <t>A 37686-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45532</v>
+        <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1591,38 +1591,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 37686-2026</t>
+          <t>A 35828-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46279</v>
+        <v>45532</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1698,31 +1698,31 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44846</v>
+        <v>45972</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2522,10 +2522,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2543,49 +2543,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,14 +2595,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45972</v>
+        <v>44846</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2627,10 +2627,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2648,42 +2648,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
         <v>46031</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44890</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44922</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3025,14 +3025,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45629</v>
+        <v>46122</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3044,22 +3044,17 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3074,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3083,49 +3078,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3135,14 +3130,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46122</v>
+        <v>45629</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3154,18 +3149,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3188,42 +3188,42 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
         <v>45007</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45189</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>45401</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>44516</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>45682</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>45543</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45543</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>44707</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45478</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44538</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44964</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45521</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45553</v>
+        <v>45638</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45638</v>
+        <v>45553</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5661,7 +5661,7 @@
         <v>44966</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45169</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45686</v>
+        <v>45529</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45495</v>
+        <v>45686</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44742</v>
+        <v>45495</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45529</v>
+        <v>44742</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6099,7 +6099,7 @@
         <v>45702</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45048</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6245,7 +6245,7 @@
         <v>44964</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6301,7 +6301,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6318,7 +6318,7 @@
         <v>44964</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6374,7 +6374,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45553</v>
+        <v>45875</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6461,10 +6461,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45596</v>
+        <v>45875</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>15.1</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6530,14 +6530,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45393</v>
+        <v>45877</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6593,7 +6593,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44896</v>
+        <v>45877</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45676</v>
+        <v>44607</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6739,7 +6739,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44700</v>
+        <v>45596</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>15.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45890</v>
+        <v>45553</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45820</v>
+        <v>45890</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6958,7 +6958,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6968,14 +6968,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45730</v>
+        <v>45393</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7031,7 +7031,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45904</v>
+        <v>44896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7060,13 +7060,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7109,7 +7104,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7123,10 +7118,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45446</v>
+        <v>45820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7139,7 +7134,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7182,7 +7177,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7196,10 +7191,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44964</v>
+        <v>45904</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7211,8 +7206,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7255,7 +7255,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44964</v>
+        <v>45730</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
         <v>45909</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45214</v>
+        <v>45676</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45083</v>
+        <v>44700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>13.1</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45103</v>
+        <v>45926</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7637,7 +7637,7 @@
         <v>45926</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 46533-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7710,7 +7710,7 @@
         <v>45926</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46533-2025</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45926</v>
+        <v>45928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7853,10 +7853,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45928</v>
+        <v>45933</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45145</v>
+        <v>45083</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.9</v>
+        <v>13.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7999,10 +7999,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45933</v>
+        <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8058,7 +8058,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45755</v>
+        <v>44964</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8131,7 +8131,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45755</v>
+        <v>44964</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45752</v>
+        <v>45214</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45752</v>
+        <v>45940</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45752</v>
+        <v>45953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45201</v>
+        <v>45103</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8496,7 +8496,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45940</v>
+        <v>45145</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45169</v>
+        <v>45755</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44977</v>
+        <v>45755</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45953</v>
+        <v>45752</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8788,7 +8788,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8798,14 +8798,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
         <v>45752</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44670</v>
+        <v>45752</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8934,7 +8934,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45313</v>
+        <v>45201</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45637</v>
+        <v>45169</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45455</v>
+        <v>44977</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9163,14 +9163,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45372</v>
+        <v>45752</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9182,13 +9182,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9231,7 +9226,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9241,14 +9236,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46007</v>
+        <v>44670</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9261,7 +9256,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9304,7 +9299,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9314,14 +9309,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9334,7 +9329,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9377,7 +9372,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9391,10 +9386,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45740</v>
+        <v>46009</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9407,7 +9402,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9450,7 +9445,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9464,10 +9459,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44970</v>
+        <v>45748</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9479,13 +9474,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9524,31 +9514,11 @@
         <v>0</v>
       </c>
       <c r="V109" s="2" t="inlineStr"/>
-      <c r="Z109">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA109">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB109">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC109">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD109">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9562,10 +9532,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45748</v>
+        <v>45313</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9578,7 +9548,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9621,7 +9591,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9635,10 +9605,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44954</v>
+        <v>45637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9651,7 +9621,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9711,7 +9681,7 @@
         <v>46031</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9767,7 +9737,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9781,10 +9751,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45313</v>
+        <v>45455</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9797,7 +9767,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9840,7 +9810,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9854,10 +9824,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44656</v>
+        <v>45372</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9869,8 +9839,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>2.6</v>
+        <v>7.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9913,7 +9888,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9927,10 +9902,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44817</v>
+        <v>46197</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9943,7 +9918,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9986,7 +9961,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10000,10 +9975,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44895</v>
+        <v>46197</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10016,7 +9991,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10059,7 +10034,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10073,10 +10048,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45455</v>
+        <v>45740</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10089,7 +10064,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10132,7 +10107,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 1489-2024</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10146,10 +10121,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45305</v>
+        <v>44970</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10161,8 +10136,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10201,11 +10181,31 @@
         <v>0</v>
       </c>
       <c r="V118" s="2" t="inlineStr"/>
+      <c r="Z118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10215,14 +10215,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44869</v>
+        <v>46088</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>10.9</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44889</v>
+        <v>44954</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>14.1</v>
+        <v>3.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10351,7 +10351,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10365,10 +10365,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44954</v>
+        <v>46246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10424,7 +10424,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44954</v>
+        <v>45313</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10497,7 +10497,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10507,14 +10507,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44998</v>
+        <v>44656</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10570,7 +10570,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10584,10 +10584,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44865</v>
+        <v>44817</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10643,7 +10643,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10653,14 +10653,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46088</v>
+        <v>44895</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10716,7 +10716,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10730,10 +10730,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44993</v>
+        <v>45455</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10789,7 +10789,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10799,14 +10799,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45244</v>
+        <v>44869</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>10.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10862,7 +10862,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10876,10 +10876,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45702</v>
+        <v>44889</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>14.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10935,7 +10935,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46197</v>
+        <v>46246</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11008,7 +11008,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11018,14 +11018,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46197</v>
+        <v>46126</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11081,7 +11081,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44938</v>
+        <v>44954</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11154,7 +11154,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11168,10 +11168,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44796</v>
+        <v>44954</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11227,7 +11227,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11237,14 +11237,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44656</v>
+        <v>44998</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11300,7 +11300,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44656</v>
+        <v>44865</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11373,7 +11373,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11383,14 +11383,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46126</v>
+        <v>44993</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11446,7 +11446,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11456,14 +11456,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45469</v>
+        <v>45244</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11519,7 +11519,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11533,10 +11533,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46246</v>
+        <v>45702</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11602,14 +11602,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44832</v>
+        <v>46216</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11665,7 +11665,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11679,10 +11679,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44607</v>
+        <v>46216</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11738,7 +11738,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11752,10 +11752,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45321</v>
+        <v>44938</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11811,7 +11811,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11825,10 +11825,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45170</v>
+        <v>44796</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11957,7 +11957,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11971,10 +11971,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45401</v>
+        <v>44656</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12030,7 +12030,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12044,10 +12044,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44992</v>
+        <v>44656</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12103,7 +12103,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12117,10 +12117,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45371</v>
+        <v>45469</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44952</v>
+        <v>46268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12249,7 +12249,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12263,10 +12263,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45204</v>
+        <v>46268</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12322,7 +12322,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12332,14 +12332,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45450</v>
+        <v>44832</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12395,7 +12395,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12409,10 +12409,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46216</v>
+        <v>46268</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12468,7 +12468,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46216</v>
+        <v>45321</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12541,7 +12541,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45016</v>
+        <v>45170</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12614,7 +12614,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12628,10 +12628,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45752</v>
+        <v>45401</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12687,7 +12687,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12701,10 +12701,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46260</v>
+        <v>46232</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12760,7 +12760,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45251</v>
+        <v>44992</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12833,7 +12833,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44670</v>
+        <v>45371</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12906,7 +12906,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12916,14 +12916,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45371</v>
+        <v>46274</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45246</v>
+        <v>44952</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13052,7 +13052,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13066,10 +13066,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46268</v>
+        <v>45204</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13125,7 +13125,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13139,10 +13139,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46268</v>
+        <v>45450</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46268</v>
+        <v>46240</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13271,7 +13271,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45280</v>
+        <v>46240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13344,7 +13344,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45324</v>
+        <v>45016</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46232</v>
+        <v>45752</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13490,7 +13490,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13504,10 +13504,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44593</v>
+        <v>45251</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13563,7 +13563,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13573,14 +13573,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46274</v>
+        <v>44670</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13636,7 +13636,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45484</v>
+        <v>45371</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44964</v>
+        <v>45246</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13782,7 +13782,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45797</v>
+        <v>45280</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13855,7 +13855,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13869,10 +13869,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46240</v>
+        <v>45324</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45740</v>
+        <v>44593</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14001,7 +14001,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14015,10 +14015,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46240</v>
+        <v>45484</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14074,7 +14074,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45797</v>
+        <v>44964</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14147,7 +14147,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14161,10 +14161,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45740</v>
+        <v>45797</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45804</v>
+        <v>45740</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14307,10 +14307,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45820</v>
+        <v>45797</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45875</v>
+        <v>45740</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14439,7 +14439,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14453,10 +14453,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45875</v>
+        <v>45804</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14512,7 +14512,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14526,10 +14526,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45877</v>
+        <v>45820</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14585,24 +14585,24 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>S 3179-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45877</v>
+        <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14658,7 +14658,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S 3179-2024</t>
+          <t>S 4371-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14672,10 +14672,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45524</v>
+        <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14728,10 +14728,10 @@
       </c>
       <c r="V180" s="2" t="inlineStr"/>
     </row>
-    <row r="181" ht="15" customHeight="1">
+    <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S 4371-2024</t>
+          <t>S 1255-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14741,14 +14741,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45587</v>
+        <v>45763</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>35.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14800,79 +14800,6 @@
         <v>0</v>
       </c>
       <c r="V181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>S 1255-2025</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D182" s="1" t="n">
-        <v>45763</v>
-      </c>
-      <c r="E182" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I182" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="J182" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" t="n">
-        <v>0</v>
-      </c>
-      <c r="M182" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="n">
-        <v>0</v>
-      </c>
-      <c r="T182" t="n">
-        <v>0</v>
-      </c>
-      <c r="U182" t="n">
-        <v>0</v>
-      </c>
-      <c r="V182" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 45507-2024</t>
+          <t>A 35828-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45578</v>
+        <v>45532</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1327,19 +1327,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>6.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
@@ -1351,378 +1351,378 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 45507-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45578</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Knärot
 Lönnlav</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 7821-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45349</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>7</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Slåtterfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 37686-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>5.1</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 35828-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45532</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Sommarfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45393</v>
+        <v>45189</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2299,21 +2299,26 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2324,10 +2329,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2336,46 +2341,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2385,14 +2390,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45349</v>
+        <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2405,7 +2410,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2414,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2432,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2441,46 +2446,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2490,14 +2495,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45972</v>
+        <v>45393</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,13 +2515,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2525,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2534,58 +2539,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,14 +2600,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44846</v>
+        <v>45349</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,7 +2620,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2624,10 +2629,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2642,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2651,46 +2656,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2704,10 +2709,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46031</v>
+        <v>45629</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2725,7 +2730,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2758,49 +2763,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44890</v>
+        <v>45007</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2829,19 +2834,14 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2875,35 +2875,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
         <v>44922</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3025,14 +3025,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46122</v>
+        <v>45972</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,23 +3045,23 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
@@ -3069,58 +3069,58 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45629</v>
+        <v>44890</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3151,20 +3151,20 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3191,46 +3191,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45007</v>
+        <v>46031</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,18 +3259,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3284,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3293,49 +3298,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3349,10 +3354,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45189</v>
+        <v>45401</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,14 +3371,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3410,42 +3415,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3455,14 +3464,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45401</v>
+        <v>46122</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3474,13 +3483,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3492,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3504,55 +3508,51 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>44516</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13811-2022</t>
+          <t>A 27760-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44649</v>
+        <v>44743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4330,7 +4330,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62452-2021</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44503</v>
+        <v>45204</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27760-2022</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44743</v>
+        <v>45596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45145</v>
+        <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 13811-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45682</v>
+        <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 62452-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45543</v>
+        <v>44503</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45543</v>
+        <v>45484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44707</v>
+        <v>44964</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5060,7 +5060,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45478</v>
+        <v>45752</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>9.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44538</v>
+        <v>45169</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44964</v>
+        <v>45246</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44964</v>
+        <v>44817</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5352,7 +5352,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45596</v>
+        <v>45016</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33875-2024</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45521</v>
+        <v>45702</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45638</v>
+        <v>44865</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45553</v>
+        <v>45752</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.1</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44966</v>
+        <v>45752</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45169</v>
+        <v>45752</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45529</v>
+        <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45686</v>
+        <v>45797</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45495</v>
+        <v>45797</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44742</v>
+        <v>45495</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6092,14 +6092,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45702</v>
+        <v>44832</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45048</v>
+        <v>45455</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44964</v>
+        <v>45313</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6301,7 +6301,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44964</v>
+        <v>45740</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6374,7 +6374,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45875</v>
+        <v>45890</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6461,10 +6461,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45875</v>
+        <v>44895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45877</v>
+        <v>44954</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6593,7 +6593,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45877</v>
+        <v>44964</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44607</v>
+        <v>44964</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45596</v>
+        <v>44964</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>15.1</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45553</v>
+        <v>44992</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45890</v>
+        <v>44869</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>10.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6958,7 +6958,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6968,14 +6968,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45393</v>
+        <v>45904</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6987,8 +6987,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7031,7 +7036,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7045,10 +7050,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44896</v>
+        <v>45469</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7061,7 +7066,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7104,7 +7109,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7118,10 +7123,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45820</v>
+        <v>45529</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7134,7 +7139,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7177,7 +7182,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7191,10 +7196,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45904</v>
+        <v>44938</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7206,13 +7211,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7255,7 +7255,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45730</v>
+        <v>45145</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
         <v>45909</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45676</v>
+        <v>45553</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44700</v>
+        <v>44889</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>14.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 33875-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45926</v>
+        <v>45521</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45926</v>
+        <v>44964</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46533-2025</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45926</v>
+        <v>45804</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45928</v>
+        <v>45321</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 46533-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7853,10 +7853,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45933</v>
+        <v>45926</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45083</v>
+        <v>44896</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>13.1</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7995,14 +7995,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45446</v>
+        <v>45393</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8058,7 +8058,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44964</v>
+        <v>45926</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8131,7 +8131,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44964</v>
+        <v>45048</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45214</v>
+        <v>45926</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45940</v>
+        <v>45401</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45953</v>
+        <v>45928</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45103</v>
+        <v>45933</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8496,7 +8496,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45145</v>
+        <v>45543</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45755</v>
+        <v>45543</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45755</v>
+        <v>45752</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45752</v>
+        <v>45940</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45752</v>
+        <v>44670</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45752</v>
+        <v>45553</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8934,7 +8934,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45201</v>
+        <v>45145</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45169</v>
+        <v>44656</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44977</v>
+        <v>45201</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9163,14 +9163,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45752</v>
+        <v>45953</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44670</v>
+        <v>45170</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46007</v>
+        <v>45371</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46009</v>
+        <v>45682</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45748</v>
+        <v>44707</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45313</v>
+        <v>45820</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45637</v>
+        <v>45169</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46031</v>
+        <v>45596</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>15.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45455</v>
+        <v>45686</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45372</v>
+        <v>45251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9839,13 +9839,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9888,7 +9883,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9902,10 +9897,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46197</v>
+        <v>44656</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9918,7 +9913,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9961,7 +9956,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9975,10 +9970,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46197</v>
+        <v>44656</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9991,7 +9986,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10034,7 +10029,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10044,14 +10039,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45740</v>
+        <v>44998</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10064,7 +10059,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10107,7 +10102,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10121,10 +10116,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44970</v>
+        <v>45214</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10136,13 +10131,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10181,31 +10171,11 @@
         <v>0</v>
       </c>
       <c r="V118" s="2" t="inlineStr"/>
-      <c r="Z118">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA118">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB118">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC118">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD118">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10215,14 +10185,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46088</v>
+        <v>45637</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10235,7 +10205,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10278,7 +10248,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10292,10 +10262,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44954</v>
+        <v>44670</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10308,7 +10278,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10351,7 +10321,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10365,10 +10335,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46246</v>
+        <v>45638</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10381,7 +10351,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10424,7 +10394,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10438,10 +10408,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45313</v>
+        <v>44977</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10454,7 +10424,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10497,7 +10467,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10511,10 +10481,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44656</v>
+        <v>45740</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10527,7 +10497,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10570,7 +10540,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10584,10 +10554,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44817</v>
+        <v>44796</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10600,7 +10570,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10643,7 +10613,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10657,10 +10627,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44895</v>
+        <v>46031</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10673,7 +10643,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10716,7 +10686,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10730,10 +10700,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45455</v>
+        <v>45372</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10745,8 +10715,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10789,7 +10764,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10799,14 +10774,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44869</v>
+        <v>46007</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10819,7 +10794,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>10.9</v>
+        <v>2.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10862,7 +10837,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10876,10 +10851,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44889</v>
+        <v>45313</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10892,7 +10867,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10935,7 +10910,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10949,10 +10924,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46246</v>
+        <v>46009</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10965,7 +10940,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11008,7 +10983,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11018,14 +10993,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46126</v>
+        <v>45748</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11038,7 +11013,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11081,7 +11056,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11095,10 +11070,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44954</v>
+        <v>44966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11111,7 +11086,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11154,7 +11129,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11164,14 +11139,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44954</v>
+        <v>45478</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11184,7 +11159,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11227,7 +11202,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11237,14 +11212,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44998</v>
+        <v>45371</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11232,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11300,7 +11275,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11314,10 +11289,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44865</v>
+        <v>44954</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11330,7 +11305,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11373,7 +11348,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11387,10 +11362,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44993</v>
+        <v>46246</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11403,7 +11378,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11446,7 +11421,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11456,14 +11431,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45244</v>
+        <v>44993</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11519,7 +11494,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11533,10 +11508,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45702</v>
+        <v>44964</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11549,7 +11524,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11592,7 +11567,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11606,10 +11581,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46216</v>
+        <v>46246</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11622,7 +11597,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11665,7 +11640,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11679,10 +11654,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46216</v>
+        <v>45450</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11695,7 +11670,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11738,7 +11713,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11752,10 +11727,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44938</v>
+        <v>44970</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11767,8 +11742,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11807,11 +11787,31 @@
         <v>0</v>
       </c>
       <c r="V140" s="2" t="inlineStr"/>
+      <c r="Z140">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA140">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB140">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC140">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD140">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11825,10 +11825,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44796</v>
+        <v>45103</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46260</v>
+        <v>44538</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11957,7 +11957,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11967,14 +11967,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44656</v>
+        <v>46088</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12030,7 +12030,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12040,14 +12040,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44656</v>
+        <v>45244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12103,7 +12103,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12117,10 +12117,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45469</v>
+        <v>45455</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46268</v>
+        <v>44954</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12249,7 +12249,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12263,10 +12263,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46268</v>
+        <v>44964</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12322,7 +12322,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12332,14 +12332,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44832</v>
+        <v>45755</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12395,7 +12395,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12409,10 +12409,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46268</v>
+        <v>45755</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12468,7 +12468,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12478,14 +12478,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45321</v>
+        <v>46126</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12541,7 +12541,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45170</v>
+        <v>45875</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12614,7 +12614,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12628,10 +12628,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45401</v>
+        <v>45875</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12687,7 +12687,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12701,10 +12701,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46232</v>
+        <v>45446</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12760,7 +12760,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44992</v>
+        <v>45877</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12833,7 +12833,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45371</v>
+        <v>45877</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12906,7 +12906,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12916,14 +12916,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46274</v>
+        <v>45676</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44952</v>
+        <v>44607</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13052,7 +13052,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13066,10 +13066,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45204</v>
+        <v>45820</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13125,7 +13125,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13139,10 +13139,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45450</v>
+        <v>44742</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46240</v>
+        <v>45730</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13271,7 +13271,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46240</v>
+        <v>44700</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13344,7 +13344,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45016</v>
+        <v>44952</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45752</v>
+        <v>45083</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>13.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13490,7 +13490,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13504,10 +13504,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45251</v>
+        <v>45280</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13563,7 +13563,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44670</v>
+        <v>45324</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13636,7 +13636,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45371</v>
+        <v>44593</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45246</v>
+        <v>46197</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13782,7 +13782,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45280</v>
+        <v>46197</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13855,7 +13855,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13869,10 +13869,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45324</v>
+        <v>46216</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44593</v>
+        <v>46216</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14001,7 +14001,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14015,10 +14015,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45484</v>
+        <v>46260</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14074,7 +14074,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44964</v>
+        <v>46268</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14147,7 +14147,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14161,10 +14161,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45797</v>
+        <v>46268</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45740</v>
+        <v>46268</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14307,10 +14307,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45797</v>
+        <v>46232</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14376,14 +14376,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45740</v>
+        <v>46274</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14439,7 +14439,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14453,10 +14453,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45804</v>
+        <v>46240</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14512,7 +14512,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14526,10 +14526,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45820</v>
+        <v>46240</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14602,7 +14602,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45763</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35828-2024</t>
+          <t>A 45507-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45532</v>
+        <v>45578</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1327,19 +1327,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.7</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
@@ -1351,271 +1351,271 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Knärot
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7821-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Slåtterfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35828-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45532</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 45507-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45578</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Knärot
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 7821-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>7</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Slåtterfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
         <v>46279</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45189</v>
+        <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2299,25 +2299,20 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2329,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2341,46 +2336,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2390,14 +2385,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44846</v>
+        <v>45349</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2410,7 +2405,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2419,10 +2414,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2437,7 +2432,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2446,46 +2441,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2495,14 +2490,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45393</v>
+        <v>45972</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,23 +2510,23 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
@@ -2539,58 +2534,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2600,14 +2595,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45349</v>
+        <v>44846</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2620,7 +2615,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2629,10 +2624,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2647,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2656,46 +2651,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,10 +2704,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45629</v>
+        <v>46031</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2730,7 +2725,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2763,49 +2758,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45007</v>
+        <v>44890</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2834,14 +2829,19 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2875,35 +2875,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
         <v>44922</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3025,14 +3025,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45972</v>
+        <v>46122</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3069,58 +3069,58 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44890</v>
+        <v>45629</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3151,21 +3151,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3191,46 +3191,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46031</v>
+        <v>45007</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,22 +3259,17 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3289,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3298,49 +3293,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3354,10 +3349,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45401</v>
+        <v>45189</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,14 +3366,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3415,46 +3410,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3464,14 +3455,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46122</v>
+        <v>45401</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3483,8 +3474,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3496,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3508,51 +3504,55 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>44516</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27760-2022</t>
+          <t>A 13811-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44743</v>
+        <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4330,7 +4330,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 62452-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45204</v>
+        <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 27760-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45596</v>
+        <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45702</v>
+        <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13811-2022</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44649</v>
+        <v>45682</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62452-2021</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44503</v>
+        <v>45543</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45484</v>
+        <v>45543</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44964</v>
+        <v>44707</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5060,7 +5060,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45752</v>
+        <v>45478</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45169</v>
+        <v>44538</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45246</v>
+        <v>44964</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44817</v>
+        <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5352,7 +5352,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45016</v>
+        <v>45596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 33875-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45702</v>
+        <v>45521</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44865</v>
+        <v>45638</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45752</v>
+        <v>45553</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>6.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45752</v>
+        <v>44966</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45752</v>
+        <v>45169</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45740</v>
+        <v>45529</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45797</v>
+        <v>45686</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45797</v>
+        <v>45495</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45495</v>
+        <v>44742</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6092,14 +6092,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44832</v>
+        <v>45702</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45455</v>
+        <v>45048</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45313</v>
+        <v>44964</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6301,7 +6301,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45740</v>
+        <v>44964</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6374,7 +6374,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45890</v>
+        <v>45875</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6461,10 +6461,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44895</v>
+        <v>45875</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44954</v>
+        <v>45877</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6593,7 +6593,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44964</v>
+        <v>45877</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44964</v>
+        <v>44607</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44964</v>
+        <v>45596</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>15.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44992</v>
+        <v>45890</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44869</v>
+        <v>45553</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>10.9</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6958,7 +6958,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6968,14 +6968,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45904</v>
+        <v>45393</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6987,13 +6987,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7036,7 +7031,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7050,10 +7045,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45469</v>
+        <v>44896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7066,7 +7061,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7109,7 +7104,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7123,10 +7118,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45529</v>
+        <v>45904</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7138,8 +7133,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44938</v>
+        <v>45676</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7255,7 +7255,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 43134-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45145</v>
+        <v>45909</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7328,7 +7328,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43134-2025</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45909</v>
+        <v>44700</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7401,7 +7401,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45553</v>
+        <v>45926</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44889</v>
+        <v>45926</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>14.1</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33875-2024</t>
+          <t>A 46533-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45521</v>
+        <v>45926</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44964</v>
+        <v>45928</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45804</v>
+        <v>45933</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45321</v>
+        <v>45446</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46533-2025</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7853,10 +7853,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45926</v>
+        <v>45820</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>7.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44896</v>
+        <v>44964</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7995,14 +7995,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45393</v>
+        <v>44964</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8058,7 +8058,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45926</v>
+        <v>45214</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8131,7 +8131,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45048</v>
+        <v>45730</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45926</v>
+        <v>45940</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45401</v>
+        <v>45103</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45928</v>
+        <v>45953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45933</v>
+        <v>45145</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8496,7 +8496,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45543</v>
+        <v>45755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45543</v>
+        <v>45755</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8659,7 +8659,7 @@
         <v>45752</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45940</v>
+        <v>45752</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8788,7 +8788,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44670</v>
+        <v>45752</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45553</v>
+        <v>45201</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8934,7 +8934,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45145</v>
+        <v>45083</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.9</v>
+        <v>13.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44656</v>
+        <v>45169</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45201</v>
+        <v>44977</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9163,14 +9163,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45953</v>
+        <v>45752</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45170</v>
+        <v>44670</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45371</v>
+        <v>46007</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45682</v>
+        <v>45313</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44707</v>
+        <v>46009</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45820</v>
+        <v>45748</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45169</v>
+        <v>45637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45596</v>
+        <v>45455</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>15.1</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45686</v>
+        <v>46031</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45251</v>
+        <v>45372</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9839,8 +9839,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9883,7 +9888,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9897,10 +9902,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44656</v>
+        <v>45740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9913,7 +9918,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9956,7 +9961,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9970,10 +9975,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44656</v>
+        <v>44970</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9985,8 +9990,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10025,11 +10035,31 @@
         <v>0</v>
       </c>
       <c r="V116" s="2" t="inlineStr"/>
+      <c r="Z116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10039,14 +10069,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44998</v>
+        <v>44954</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10059,7 +10089,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10102,7 +10132,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10116,10 +10146,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45214</v>
+        <v>45313</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10132,7 +10162,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10175,7 +10205,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10185,14 +10215,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45637</v>
+        <v>46088</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10205,7 +10235,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10248,7 +10278,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10262,10 +10292,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44670</v>
+        <v>44656</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10278,7 +10308,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10321,7 +10351,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10335,10 +10365,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45638</v>
+        <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10351,7 +10381,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10394,7 +10424,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10408,10 +10438,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44977</v>
+        <v>44895</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10424,7 +10454,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10467,7 +10497,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10481,10 +10511,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45740</v>
+        <v>45455</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10497,7 +10527,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10540,7 +10570,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10554,10 +10584,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44796</v>
+        <v>44869</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10570,7 +10600,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.7</v>
+        <v>10.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10613,7 +10643,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10627,10 +10657,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46031</v>
+        <v>44889</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10643,7 +10673,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3</v>
+        <v>14.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10686,7 +10716,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10696,14 +10726,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45372</v>
+        <v>46126</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10715,13 +10745,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10764,7 +10789,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10774,14 +10799,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46007</v>
+        <v>44954</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10794,7 +10819,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10837,7 +10862,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10851,10 +10876,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45313</v>
+        <v>44954</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10867,7 +10892,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10910,7 +10935,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10920,14 +10945,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46009</v>
+        <v>44998</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10940,7 +10965,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10983,7 +11008,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10997,10 +11022,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45748</v>
+        <v>44865</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11013,7 +11038,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11056,7 +11081,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11070,10 +11095,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44966</v>
+        <v>46197</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11086,7 +11111,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11129,7 +11154,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11139,14 +11164,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45478</v>
+        <v>44993</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11159,7 +11184,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11202,7 +11227,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11216,10 +11241,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45371</v>
+        <v>46197</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11232,7 +11257,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11275,7 +11300,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11285,14 +11310,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44954</v>
+        <v>45244</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11305,7 +11330,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11348,7 +11373,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11362,10 +11387,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46246</v>
+        <v>45702</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11378,7 +11403,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11421,7 +11446,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11435,10 +11460,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44993</v>
+        <v>44938</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11451,7 +11476,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11494,7 +11519,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11508,10 +11533,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44964</v>
+        <v>44796</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11524,7 +11549,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11567,7 +11592,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11581,10 +11606,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46246</v>
+        <v>44656</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11597,7 +11622,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11640,7 +11665,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11654,10 +11679,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45450</v>
+        <v>44656</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11670,7 +11695,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11713,7 +11738,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11727,10 +11752,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44970</v>
+        <v>45469</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11742,13 +11767,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11787,31 +11807,11 @@
         <v>0</v>
       </c>
       <c r="V140" s="2" t="inlineStr"/>
-      <c r="Z140">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA140">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB140">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC140">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD140">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11821,14 +11821,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45103</v>
+        <v>44832</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44538</v>
+        <v>46216</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11957,7 +11957,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11967,14 +11967,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46088</v>
+        <v>46216</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12030,7 +12030,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12040,14 +12040,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45244</v>
+        <v>45321</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12103,7 +12103,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12117,10 +12117,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45455</v>
+        <v>45170</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44954</v>
+        <v>46260</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12249,7 +12249,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12263,10 +12263,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44964</v>
+        <v>45401</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12336,10 +12336,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45755</v>
+        <v>44992</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12395,7 +12395,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12409,10 +12409,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45755</v>
+        <v>45371</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12468,7 +12468,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12478,14 +12478,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46126</v>
+        <v>46268</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12541,7 +12541,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45875</v>
+        <v>46268</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12614,7 +12614,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12628,10 +12628,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45875</v>
+        <v>44952</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12687,7 +12687,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12701,10 +12701,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45446</v>
+        <v>46268</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12760,7 +12760,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45877</v>
+        <v>45204</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12833,7 +12833,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45877</v>
+        <v>45450</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12906,7 +12906,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45676</v>
+        <v>45016</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44607</v>
+        <v>45752</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13052,7 +13052,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13066,10 +13066,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45820</v>
+        <v>46232</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13125,7 +13125,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13139,10 +13139,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44742</v>
+        <v>45251</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45730</v>
+        <v>44670</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13271,7 +13271,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44700</v>
+        <v>45371</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13344,7 +13344,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13354,14 +13354,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44952</v>
+        <v>46274</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45083</v>
+        <v>45246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>13.1</v>
+        <v>0.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13490,7 +13490,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13504,10 +13504,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45280</v>
+        <v>46240</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13563,7 +13563,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45324</v>
+        <v>46240</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13636,7 +13636,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44593</v>
+        <v>45280</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46197</v>
+        <v>45324</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13782,7 +13782,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46197</v>
+        <v>44593</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13855,7 +13855,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13869,10 +13869,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46216</v>
+        <v>45484</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46216</v>
+        <v>44964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14001,7 +14001,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14015,10 +14015,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46260</v>
+        <v>46246</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14074,7 +14074,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46268</v>
+        <v>45797</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14147,7 +14147,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14161,10 +14161,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46268</v>
+        <v>45740</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46268</v>
+        <v>45797</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14307,10 +14307,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46232</v>
+        <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14376,14 +14376,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46274</v>
+        <v>46246</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14439,7 +14439,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14453,10 +14453,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46240</v>
+        <v>45804</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14512,7 +14512,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14526,10 +14526,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46240</v>
+        <v>45820</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14602,7 +14602,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45763</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 45507-2024</t>
+          <t>A 7821-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45578</v>
+        <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1327,22 +1327,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1351,378 +1351,378 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Slåtterfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 35828-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45532</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37686-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 45507-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45578</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Knärot
 Lönnlav</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 7821-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Slåtterfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35828-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45532</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Sommarfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 37686-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Sommarfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45393</v>
+        <v>44846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,20 +2300,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2324,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2336,46 +2336,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2385,14 +2385,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45349</v>
+        <v>44890</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2404,17 +2404,22 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2429,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2441,46 +2446,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2490,14 +2495,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45972</v>
+        <v>46031</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2509,8 +2514,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2519,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2537,55 +2547,55 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,14 +2605,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44846</v>
+        <v>45349</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,7 +2625,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2624,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2642,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2651,46 +2661,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 62232-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2704,10 +2714,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46031</v>
+        <v>44922</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2719,13 +2729,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2734,13 +2739,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2752,55 +2757,55 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2810,14 +2815,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44890</v>
+        <v>46122</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2829,13 +2834,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2868,49 +2868,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 62232-2022</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2920,14 +2920,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44922</v>
+        <v>45972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2973,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2984,38 +2984,38 @@
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46122</v>
+        <v>45393</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3078,49 +3078,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45629</v>
+        <v>45401</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3151,23 +3151,23 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3191,46 +3191,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3244,10 +3248,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45007</v>
+        <v>45629</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,18 +3263,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3284,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3296,46 +3305,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3349,10 +3358,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45189</v>
+        <v>45007</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,25 +3373,20 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3394,10 +3398,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3410,42 +3414,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3459,10 +3463,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45401</v>
+        <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3476,14 +3480,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3520,39 +3524,35 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55888-2021</t>
+          <t>A 65493-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44476</v>
+        <v>44516</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3697,8 +3697,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3741,7 +3746,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 65493-2021</t>
+          <t>A 55888-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3755,10 +3760,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44516</v>
+        <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3770,13 +3775,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45145</v>
+        <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45682</v>
+        <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4851,14 +4851,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45543</v>
+        <v>44832</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45543</v>
+        <v>45455</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44707</v>
+        <v>45702</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5060,7 +5060,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45478</v>
+        <v>44895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44538</v>
+        <v>44964</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5223,7 +5223,7 @@
         <v>44964</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5296,7 +5296,7 @@
         <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5352,7 +5352,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45596</v>
+        <v>44869</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33875-2024</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45521</v>
+        <v>45469</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45638</v>
+        <v>45529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45553</v>
+        <v>45740</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44966</v>
+        <v>45797</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45169</v>
+        <v>45797</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45529</v>
+        <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45686</v>
+        <v>46031</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45495</v>
+        <v>45553</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44742</v>
+        <v>44889</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>14.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45702</v>
+        <v>45890</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 33875-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45048</v>
+        <v>45521</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6245,7 +6245,7 @@
         <v>44964</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6301,7 +6301,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44964</v>
+        <v>45321</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6374,7 +6374,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45875</v>
+        <v>44896</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6457,14 +6457,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45875</v>
+        <v>45393</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45877</v>
+        <v>45904</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6549,8 +6549,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6593,7 +6598,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 43134-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6607,10 +6612,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45877</v>
+        <v>45909</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6623,7 +6628,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6666,7 +6671,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6680,10 +6685,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44607</v>
+        <v>45804</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6696,7 +6701,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6739,7 +6744,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 46533-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6753,10 +6758,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45596</v>
+        <v>45926</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6769,7 +6774,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>15.1</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6812,7 +6817,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6826,10 +6831,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45890</v>
+        <v>45926</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6842,7 +6847,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6885,7 +6890,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6899,10 +6904,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45553</v>
+        <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6915,7 +6920,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6958,7 +6963,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6968,14 +6973,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45393</v>
+        <v>44670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6988,7 +6993,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7031,7 +7036,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7045,10 +7050,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44896</v>
+        <v>45553</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7061,7 +7066,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7104,7 +7109,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7118,10 +7123,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45904</v>
+        <v>45928</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7131,11 +7136,6 @@
       <c r="G77" t="inlineStr">
         <is>
           <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -7182,7 +7182,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45676</v>
+        <v>45933</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7255,7 +7255,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43134-2025</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45909</v>
+        <v>44656</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7328,7 +7328,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7338,14 +7338,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44700</v>
+        <v>46088</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7401,7 +7401,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45926</v>
+        <v>45940</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45926</v>
+        <v>44707</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46533-2025</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45926</v>
+        <v>45596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>15.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45928</v>
+        <v>45251</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7703,14 +7703,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45933</v>
+        <v>44998</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45446</v>
+        <v>45953</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45820</v>
+        <v>46126</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.7</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44964</v>
+        <v>45638</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7999,10 +7999,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44964</v>
+        <v>44977</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8058,7 +8058,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45214</v>
+        <v>45204</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8131,7 +8131,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45730</v>
+        <v>45596</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45940</v>
+        <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45103</v>
+        <v>45820</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45953</v>
+        <v>45820</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8433,14 +8433,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45145</v>
+        <v>46007</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8496,7 +8496,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45755</v>
+        <v>46009</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45755</v>
+        <v>45748</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45752</v>
+        <v>45730</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8725,14 +8725,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
         <v>45752</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8788,7 +8788,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45752</v>
+        <v>45169</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45201</v>
+        <v>45246</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>45083</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45169</v>
+        <v>45016</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44977</v>
+        <v>44865</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9163,14 +9163,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
         <v>45752</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>9.6</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44670</v>
+        <v>45752</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46007</v>
+        <v>45752</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45313</v>
+        <v>45495</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46009</v>
+        <v>45313</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45748</v>
+        <v>44954</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45637</v>
+        <v>44992</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45455</v>
+        <v>44938</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46031</v>
+        <v>45145</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45372</v>
+        <v>45048</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9839,13 +9839,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9888,7 +9883,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9902,10 +9897,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45740</v>
+        <v>45401</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9961,7 +9956,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9975,10 +9970,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44970</v>
+        <v>45543</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9990,13 +9985,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10035,31 +10025,11 @@
         <v>0</v>
       </c>
       <c r="V116" s="2" t="inlineStr"/>
-      <c r="Z116">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA116">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB116">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC116">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD116">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10073,10 +10043,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44954</v>
+        <v>45543</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10089,7 +10059,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10132,7 +10102,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10146,10 +10116,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45313</v>
+        <v>45875</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10162,7 +10132,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10205,7 +10175,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10215,14 +10185,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46088</v>
+        <v>45875</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10235,7 +10205,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10278,7 +10248,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10292,10 +10262,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44656</v>
+        <v>45752</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10308,7 +10278,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10351,7 +10321,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10365,10 +10335,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44817</v>
+        <v>45877</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10381,7 +10351,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10424,7 +10394,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10438,10 +10408,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44895</v>
+        <v>46197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10454,7 +10424,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10497,7 +10467,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10511,10 +10481,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45455</v>
+        <v>45877</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10527,7 +10497,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10570,7 +10540,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10584,10 +10554,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44869</v>
+        <v>46197</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10600,7 +10570,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>10.9</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10643,7 +10613,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10657,10 +10627,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44889</v>
+        <v>45145</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10673,7 +10643,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>14.1</v>
+        <v>4.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10716,7 +10686,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10726,14 +10696,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46126</v>
+        <v>45201</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10746,7 +10716,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10789,7 +10759,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10803,10 +10773,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44954</v>
+        <v>45170</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10819,7 +10789,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10862,7 +10832,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10876,10 +10846,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44954</v>
+        <v>45371</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10892,7 +10862,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10935,7 +10905,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10945,14 +10915,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44998</v>
+        <v>45682</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10965,7 +10935,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11008,7 +10978,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11022,10 +10992,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44865</v>
+        <v>45169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11038,7 +11008,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11081,7 +11051,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11095,10 +11065,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46197</v>
+        <v>45686</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11111,7 +11081,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11154,7 +11124,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11168,10 +11138,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44993</v>
+        <v>44656</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11184,7 +11154,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11227,7 +11197,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11241,10 +11211,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46197</v>
+        <v>44656</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11227,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11300,7 +11270,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11310,14 +11280,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45244</v>
+        <v>45214</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11330,7 +11300,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11373,7 +11343,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11387,10 +11357,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45702</v>
+        <v>45637</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11403,7 +11373,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11446,7 +11416,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11460,10 +11430,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44938</v>
+        <v>44670</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11446,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11519,7 +11489,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11533,10 +11503,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44796</v>
+        <v>46216</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11549,7 +11519,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11592,7 +11562,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11606,10 +11576,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44656</v>
+        <v>46216</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11622,7 +11592,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11665,7 +11635,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11679,10 +11649,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44656</v>
+        <v>46260</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11695,7 +11665,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11738,7 +11708,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11752,10 +11722,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45469</v>
+        <v>45740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11768,7 +11738,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11811,7 +11781,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11821,14 +11791,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44832</v>
+        <v>44796</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11841,7 +11811,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11884,7 +11854,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11898,10 +11868,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46216</v>
+        <v>46268</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11914,7 +11884,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11957,7 +11927,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11971,10 +11941,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46216</v>
+        <v>45372</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11986,8 +11956,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12030,7 +12005,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12044,10 +12019,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45321</v>
+        <v>46268</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12060,7 +12035,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12103,7 +12078,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12117,10 +12092,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45170</v>
+        <v>45313</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12133,7 +12108,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12176,7 +12151,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12190,10 +12165,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46260</v>
+        <v>46268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12206,7 +12181,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12249,7 +12224,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12263,10 +12238,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45401</v>
+        <v>46232</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12279,7 +12254,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12322,7 +12297,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12332,14 +12307,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44992</v>
+        <v>46274</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12352,7 +12327,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12395,7 +12370,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12409,10 +12384,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45371</v>
+        <v>44966</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12425,7 +12400,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12468,7 +12443,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12478,14 +12453,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46268</v>
+        <v>45478</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12498,7 +12473,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12541,7 +12516,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12555,10 +12530,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46268</v>
+        <v>46240</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12571,7 +12546,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12614,7 +12589,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12628,10 +12603,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44952</v>
+        <v>46240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12644,7 +12619,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12687,7 +12662,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12701,10 +12676,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46268</v>
+        <v>45371</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12717,7 +12692,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12760,7 +12735,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12774,10 +12749,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45204</v>
+        <v>44954</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12790,7 +12765,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12833,7 +12808,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12847,10 +12822,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45450</v>
+        <v>44993</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12863,7 +12838,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12906,7 +12881,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12920,10 +12895,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45016</v>
+        <v>44964</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12936,7 +12911,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12979,7 +12954,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12993,10 +12968,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45752</v>
+        <v>45450</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13009,7 +12984,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13052,7 +13027,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13066,10 +13041,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46232</v>
+        <v>46246</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13082,7 +13057,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13125,7 +13100,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13139,10 +13114,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45251</v>
+        <v>44970</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13154,8 +13129,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13194,11 +13174,31 @@
         <v>0</v>
       </c>
       <c r="V159" s="2" t="inlineStr"/>
+      <c r="Z159">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA159">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB159">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC159">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD159">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44670</v>
+        <v>45103</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13271,7 +13271,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45371</v>
+        <v>44538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13344,7 +13344,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46274</v>
+        <v>45244</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45246</v>
+        <v>46246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13490,7 +13490,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13504,10 +13504,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46240</v>
+        <v>45455</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13563,7 +13563,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46240</v>
+        <v>44954</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13636,7 +13636,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45280</v>
+        <v>44964</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45324</v>
+        <v>45755</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13782,7 +13782,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44593</v>
+        <v>45755</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13855,7 +13855,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13869,10 +13869,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45484</v>
+        <v>45446</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44964</v>
+        <v>45676</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14001,7 +14001,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14015,10 +14015,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46246</v>
+        <v>44742</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14074,7 +14074,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45797</v>
+        <v>44700</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14147,7 +14147,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14161,10 +14161,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45740</v>
+        <v>44952</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45797</v>
+        <v>45280</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14307,10 +14307,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45740</v>
+        <v>45324</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46246</v>
+        <v>44593</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14439,7 +14439,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14453,10 +14453,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45804</v>
+        <v>45484</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14512,7 +14512,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14526,10 +14526,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45820</v>
+        <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14602,7 +14602,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45763</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45532</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45578</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>44890</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>46031</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>45349</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44922</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>46122</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45393</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>45401</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45629</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>45007</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44516</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>44832</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45455</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45702</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>44895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44964</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44964</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44869</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45469</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>45740</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45797</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45797</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>46031</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>45553</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>44889</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45890</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45521</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44964</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45321</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44896</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45393</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45904</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45909</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45804</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45926</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45926</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>45553</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45928</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45933</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>44656</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>46088</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45940</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44707</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>45596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>45251</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44998</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45953</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>46126</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45638</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44977</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45204</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45596</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>45820</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>45820</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>46007</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>46009</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>45748</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45730</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45752</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45169</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>45246</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45083</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45016</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>44865</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45752</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45752</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45752</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45495</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45313</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44954</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>44992</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44938</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45145</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45048</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45401</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45543</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45543</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45875</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45875</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>45752</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45877</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45877</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46197</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45145</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45201</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45170</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45371</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45682</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45686</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>44656</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44656</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45214</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45637</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44670</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>46216</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46216</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>46260</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>44796</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>46268</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45372</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46268</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45313</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>46268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>46232</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>46274</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44966</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45478</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>46240</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>46240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>45371</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44954</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>44993</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44964</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45450</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>46246</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44970</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45103</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45244</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>46246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45455</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44954</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44964</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45755</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45755</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45446</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45676</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44742</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44700</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44952</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45280</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45324</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44593</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45484</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45763</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45532</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45578</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>44890</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>46031</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>45349</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44922</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>46122</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45393</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>45401</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45629</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>45007</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44516</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>44832</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45455</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45702</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>44895</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44964</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44964</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44869</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45469</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>45740</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45797</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45797</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>46031</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>45553</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>44889</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45890</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45521</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44964</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45321</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44896</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45393</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45904</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45909</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45804</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45926</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45926</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>45553</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45928</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45933</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>44656</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>46088</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45940</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44707</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>45596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>45251</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44998</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45953</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>46126</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45638</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44977</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45204</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45596</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>45820</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>45820</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>46007</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>46009</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>45748</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45730</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45752</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45169</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>45246</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45083</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45016</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>44865</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45752</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45752</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45752</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45495</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45313</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44954</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>44992</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44938</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45145</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45048</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45401</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45543</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45543</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45875</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45875</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>45752</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45877</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45877</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46197</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45145</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45201</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45170</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45371</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45682</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45686</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>44656</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44656</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45214</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45637</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44670</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>46216</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46216</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>46260</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>44796</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>46268</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45372</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46268</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45313</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>46268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>46232</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>46274</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44966</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45478</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>46240</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>46240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>45371</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44954</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>44993</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44964</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45450</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>46246</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44970</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45103</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45244</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>46246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45455</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44954</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44964</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45755</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45755</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45446</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45676</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44742</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44700</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44952</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45280</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45324</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44593</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45484</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45763</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE181"/>
+  <dimension ref="A1:AE182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7821-2024</t>
+          <t>A 45507-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45349</v>
+        <v>45578</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1327,22 +1327,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1351,378 +1351,378 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Knärot
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7821-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>9</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Slåtterfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 35828-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45532</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>6.7</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 37686-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>5.1</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 45507-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45578</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Knärot
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44846</v>
+        <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,19 +2300,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2336,46 +2336,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44890</v>
+        <v>45189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,24 +2406,24 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2434,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2450,42 +2450,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46031</v>
+        <v>45401</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,23 +2516,23 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2547,55 +2547,59 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2605,14 +2609,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45349</v>
+        <v>46031</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2624,8 +2628,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2658,49 +2667,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 62232-2022</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2714,10 +2723,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44922</v>
+        <v>44890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2729,11 +2738,16 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2745,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2754,10 +2768,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2766,46 +2780,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2815,14 +2829,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46122</v>
+        <v>45972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2835,23 +2849,23 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -2859,58 +2873,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2920,14 +2934,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45972</v>
+        <v>45349</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2940,7 +2954,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2949,13 +2963,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2967,55 +2981,55 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3029,10 +3043,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45393</v>
+        <v>46122</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,13 +3059,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3078,49 +3092,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3148,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45401</v>
+        <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3149,16 +3163,11 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3195,46 +3204,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 62232-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3248,10 +3253,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45629</v>
+        <v>44922</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3263,13 +3268,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3278,13 +3278,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3296,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3309,42 +3309,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45007</v>
+        <v>45629</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3373,18 +3373,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3398,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3410,46 +3415,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3463,10 +3468,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45189</v>
+        <v>45007</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3478,25 +3483,20 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3508,10 +3508,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3524,35 +3524,35 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 65493-2021</t>
+          <t>A 55888-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44516</v>
+        <v>44476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3697,13 +3697,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3746,7 +3741,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55888-2021</t>
+          <t>A 65493-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3760,10 +3755,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44476</v>
+        <v>44516</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3775,8 +3770,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45702</v>
+        <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44817</v>
+        <v>45682</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4851,14 +4851,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44832</v>
+        <v>45543</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45455</v>
+        <v>45543</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45702</v>
+        <v>44707</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5060,7 +5060,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44895</v>
+        <v>45478</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44964</v>
+        <v>44538</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5223,7 +5223,7 @@
         <v>44964</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5296,7 +5296,7 @@
         <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5352,7 +5352,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44869</v>
+        <v>45484</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10.9</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45469</v>
+        <v>44964</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5508,14 +5508,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45529</v>
+        <v>46007</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45740</v>
+        <v>46009</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24440-2025</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45797</v>
+        <v>45596</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 24440-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5734,7 +5734,7 @@
         <v>45797</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5807,7 +5807,7 @@
         <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46031</v>
+        <v>45797</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45553</v>
+        <v>45890</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44889</v>
+        <v>45740</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45890</v>
+        <v>45804</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
         <v>45521</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44964</v>
+        <v>45638</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6301,7 +6301,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45321</v>
+        <v>45904</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6330,8 +6330,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6374,7 +6379,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6388,10 +6393,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44896</v>
+        <v>45553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6404,7 +6409,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6447,7 +6452,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6457,14 +6462,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45393</v>
+        <v>44966</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6477,7 +6482,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6520,7 +6525,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 43134-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6534,10 +6539,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45904</v>
+        <v>45909</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6547,11 +6552,6 @@
       <c r="G69" t="inlineStr">
         <is>
           <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -6598,7 +6598,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43134-2025</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45909</v>
+        <v>45820</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6671,7 +6671,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45804</v>
+        <v>45748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6744,7 +6744,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46533-2025</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45926</v>
+        <v>45169</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45926</v>
+        <v>45529</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
         <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44670</v>
+        <v>45926</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 46533-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45553</v>
+        <v>45926</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>45928</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45933</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44656</v>
+        <v>45686</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7328,7 +7328,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7338,14 +7338,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46088</v>
+        <v>45940</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7401,7 +7401,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45940</v>
+        <v>45495</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44707</v>
+        <v>45953</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45596</v>
+        <v>44742</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>15.1</v>
+        <v>3.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45251</v>
+        <v>46031</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7703,14 +7703,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44998</v>
+        <v>45702</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45953</v>
+        <v>45875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46126</v>
+        <v>45875</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45638</v>
+        <v>45877</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7999,10 +7999,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44977</v>
+        <v>45877</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8058,7 +8058,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45204</v>
+        <v>45048</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8131,7 +8131,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45596</v>
+        <v>44964</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44607</v>
+        <v>44964</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45820</v>
+        <v>45596</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.7</v>
+        <v>15.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45820</v>
+        <v>45553</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8433,14 +8433,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46007</v>
+        <v>45393</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8496,7 +8496,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46009</v>
+        <v>44896</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45748</v>
+        <v>45676</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45730</v>
+        <v>44700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45752</v>
+        <v>46088</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>9.6</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8788,7 +8788,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45169</v>
+        <v>45446</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45246</v>
+        <v>44964</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8934,7 +8934,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45083</v>
+        <v>44964</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>13.1</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45016</v>
+        <v>45214</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44865</v>
+        <v>45103</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45752</v>
+        <v>45145</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45752</v>
+        <v>45755</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45752</v>
+        <v>45755</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45495</v>
+        <v>45752</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45313</v>
+        <v>45752</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44954</v>
+        <v>45752</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44992</v>
+        <v>45201</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9674,14 +9674,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44938</v>
+        <v>46126</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45145</v>
+        <v>45169</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45048</v>
+        <v>44977</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9883,7 +9883,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9893,14 +9893,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45401</v>
+        <v>45752</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>9.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9956,7 +9956,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45543</v>
+        <v>44607</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10029,7 +10029,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10043,10 +10043,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45543</v>
+        <v>44670</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45875</v>
+        <v>45313</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10175,7 +10175,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45875</v>
+        <v>45820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10248,7 +10248,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10262,10 +10262,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45752</v>
+        <v>45730</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45877</v>
+        <v>45637</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46197</v>
+        <v>45455</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45877</v>
+        <v>45083</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>13.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10540,7 +10540,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28517-2026</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46197</v>
+        <v>45372</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10569,8 +10569,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10613,7 +10618,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10627,10 +10632,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45145</v>
+        <v>45740</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10643,7 +10648,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10686,7 +10691,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10700,10 +10705,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45201</v>
+        <v>44970</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10715,8 +10720,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10755,11 +10765,31 @@
         <v>0</v>
       </c>
       <c r="V126" s="2" t="inlineStr"/>
+      <c r="Z126">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA126">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB126">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC126">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD126">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10773,10 +10803,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45170</v>
+        <v>44954</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10789,7 +10819,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10832,7 +10862,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10846,10 +10876,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45371</v>
+        <v>45313</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10862,7 +10892,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10905,7 +10935,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10919,10 +10949,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45682</v>
+        <v>44656</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10935,7 +10965,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10978,7 +11008,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10992,10 +11022,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45169</v>
+        <v>44817</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11008,7 +11038,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11051,7 +11081,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11065,10 +11095,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45686</v>
+        <v>44895</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11081,7 +11111,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11124,7 +11154,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11138,10 +11168,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44656</v>
+        <v>45455</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11154,7 +11184,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11197,7 +11227,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11211,10 +11241,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44656</v>
+        <v>44869</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11227,7 +11257,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11270,7 +11300,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11284,10 +11314,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45214</v>
+        <v>44889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11300,7 +11330,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.3</v>
+        <v>14.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11343,7 +11373,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11357,10 +11387,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45637</v>
+        <v>44954</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11373,7 +11403,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11416,7 +11446,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11430,10 +11460,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44670</v>
+        <v>44954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11446,7 +11476,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11489,7 +11519,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11499,14 +11529,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46216</v>
+        <v>44998</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11519,7 +11549,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11562,7 +11592,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11576,10 +11606,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46216</v>
+        <v>44865</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11592,7 +11622,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11635,7 +11665,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11649,10 +11679,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46260</v>
+        <v>44993</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11665,7 +11695,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11708,7 +11738,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11718,14 +11748,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45740</v>
+        <v>45244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11781,7 +11811,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11795,10 +11825,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44796</v>
+        <v>45702</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11811,7 +11841,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11854,7 +11884,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 28517-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11868,10 +11898,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46268</v>
+        <v>46197</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11884,7 +11914,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11927,7 +11957,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11941,10 +11971,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45372</v>
+        <v>46197</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11956,13 +11986,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12005,7 +12030,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 36413-2026</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12019,10 +12044,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46268</v>
+        <v>44938</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12078,7 +12103,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12092,10 +12117,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45313</v>
+        <v>44796</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12108,7 +12133,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12151,7 +12176,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12165,10 +12190,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46268</v>
+        <v>44656</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12181,7 +12206,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12224,7 +12249,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12238,10 +12263,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46232</v>
+        <v>44656</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12254,7 +12279,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12297,7 +12322,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12307,14 +12332,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46274</v>
+        <v>45469</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12327,7 +12352,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12370,7 +12395,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12380,14 +12405,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44966</v>
+        <v>44832</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12400,7 +12425,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12443,7 +12468,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12453,14 +12478,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45478</v>
+        <v>45321</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12473,7 +12498,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12516,7 +12541,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12530,10 +12555,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46240</v>
+        <v>45170</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12546,7 +12571,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12589,7 +12614,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12603,10 +12628,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46240</v>
+        <v>46216</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12619,7 +12644,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12662,7 +12687,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12676,10 +12701,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45371</v>
+        <v>46216</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12692,7 +12717,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12735,7 +12760,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12749,10 +12774,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44954</v>
+        <v>45401</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12765,7 +12790,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12808,7 +12833,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12822,10 +12847,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44993</v>
+        <v>44992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12838,7 +12863,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12881,7 +12906,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12895,10 +12920,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44964</v>
+        <v>46260</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12911,7 +12936,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12954,7 +12979,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12968,10 +12993,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45450</v>
+        <v>45371</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12984,7 +13009,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13027,7 +13052,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13041,10 +13066,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46246</v>
+        <v>44952</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13057,7 +13082,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13100,7 +13125,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13114,10 +13139,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44970</v>
+        <v>45204</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13129,13 +13154,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13174,31 +13194,11 @@
         <v>0</v>
       </c>
       <c r="V159" s="2" t="inlineStr"/>
-      <c r="Z159">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA159">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB159">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC159">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD159">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45103</v>
+        <v>46268</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13271,7 +13271,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44538</v>
+        <v>46268</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13344,7 +13344,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13354,14 +13354,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45244</v>
+        <v>45450</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 36413-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46246</v>
+        <v>46268</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13490,7 +13490,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13504,10 +13504,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45455</v>
+        <v>45016</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13563,7 +13563,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44954</v>
+        <v>45752</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13636,7 +13636,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44964</v>
+        <v>45251</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45755</v>
+        <v>44670</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13782,7 +13782,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45755</v>
+        <v>46232</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13855,7 +13855,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13869,10 +13869,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45446</v>
+        <v>45371</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45676</v>
+        <v>45246</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14001,7 +14001,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14011,14 +14011,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44742</v>
+        <v>46274</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14074,7 +14074,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44700</v>
+        <v>45280</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14147,7 +14147,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14161,10 +14161,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44952</v>
+        <v>45324</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45280</v>
+        <v>46240</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14307,10 +14307,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45324</v>
+        <v>46240</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14383,7 +14383,7 @@
         <v>44593</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14453,10 +14453,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45484</v>
+        <v>46246</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14512,7 +14512,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14526,10 +14526,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44964</v>
+        <v>46246</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14585,24 +14585,24 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S 3179-2024</t>
+          <t>A 40217-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45524</v>
+        <v>46293</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14658,148 +14658,221 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
+          <t>S 3179-2024</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>45524</v>
+      </c>
+      <c r="E180" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="n">
+        <v>0</v>
+      </c>
+      <c r="V180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181" ht="15" customHeight="1">
+      <c r="A181" t="inlineStr">
+        <is>
           <t>S 4371-2024</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D180" s="1" t="n">
+      <c r="D181" s="1" t="n">
         <v>45587</v>
       </c>
-      <c r="E180" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I180" t="n">
+      <c r="E181" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
         <v>1.5</v>
       </c>
-      <c r="J180" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" t="n">
-        <v>0</v>
-      </c>
-      <c r="M180" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" t="n">
-        <v>0</v>
-      </c>
-      <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0</v>
-      </c>
-      <c r="S180" t="n">
-        <v>0</v>
-      </c>
-      <c r="T180" t="n">
-        <v>0</v>
-      </c>
-      <c r="U180" t="n">
-        <v>0</v>
-      </c>
-      <c r="V180" s="2" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>S 1255-2025</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D181" s="1" t="n">
+      <c r="D182" s="1" t="n">
         <v>45763</v>
       </c>
-      <c r="E181" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I181" t="n">
+      <c r="E182" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
         <v>35.7</v>
       </c>
-      <c r="J181" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" t="n">
-        <v>0</v>
-      </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
-        <v>0</v>
-      </c>
-      <c r="V181" s="2" t="inlineStr"/>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="n">
+        <v>0</v>
+      </c>
+      <c r="V182" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 45507-2024</t>
+          <t>A 7821-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45578</v>
+        <v>45349</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1327,22 +1327,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1351,378 +1351,378 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Slåtterfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 35828-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45532</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37686-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 45507-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45578</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Knärot
 Lönnlav</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 7821-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Slåtterfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 35828-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45532</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Sommarfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 37686-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Sommarfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45349</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45393</v>
+        <v>44846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,20 +2300,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2324,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2336,39 +2336,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
         <v>45189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45401</v>
+        <v>44890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2544,10 +2544,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2560,39 +2560,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
@@ -2616,7 +2612,7 @@
         <v>46031</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2709,7 +2705,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2719,14 +2715,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44890</v>
+        <v>45349</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2738,23 +2734,18 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2768,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2780,46 +2771,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 62232-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2829,14 +2820,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45972</v>
+        <v>44922</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2849,7 +2840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2882,7 +2873,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2893,38 +2884,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,14 +2925,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45349</v>
+        <v>45401</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2953,20 +2944,25 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2981,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2990,46 +2986,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46122</v>
+        <v>45972</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3059,23 +3059,23 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
@@ -3083,58 +3083,58 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44846</v>
+        <v>46122</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3188,58 +3188,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62232-2022</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3249,14 +3249,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44922</v>
+        <v>45393</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3284,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3293,10 +3293,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3309,35 +3309,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
         <v>45629</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45007</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>44516</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44707</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44707</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35245-2023</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45145</v>
+        <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3837-2025</t>
+          <t>A 39353-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45682</v>
+        <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37797-2024</t>
+          <t>A 7268-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45543</v>
+        <v>45702</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37798-2024</t>
+          <t>A 29527-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45543</v>
+        <v>45484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21687-2022</t>
+          <t>A 42872-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4997,14 +4997,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44707</v>
+        <v>44832</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28791-2024</t>
+          <t>A 23787-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45478</v>
+        <v>45455</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 71048-2021</t>
+          <t>A 6209-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44538</v>
+        <v>44964</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6210-2023</t>
+          <t>A 57025-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44964</v>
+        <v>44895</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6212-2023</t>
+          <t>A 6210-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5296,7 +5296,7 @@
         <v>44964</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5352,7 +5352,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29527-2024</t>
+          <t>A 6212-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45484</v>
+        <v>44964</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6209-2023</t>
+          <t>A 6214-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5442,7 +5442,7 @@
         <v>44964</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62586-2025</t>
+          <t>A 52385-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5508,14 +5508,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46007</v>
+        <v>44869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>10.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62956-2025</t>
+          <t>A 26757-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46009</v>
+        <v>45469</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49734-2024</t>
+          <t>A 14033-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45596</v>
+        <v>45740</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>45797</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14033-2025</t>
+          <t>A 24439-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45740</v>
+        <v>45797</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24439-2025</t>
+          <t>A 35113-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45797</v>
+        <v>45529</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39590-2025</t>
+          <t>A 14029-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45890</v>
+        <v>45740</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14029-2025</t>
+          <t>A 39590-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45740</v>
+        <v>45890</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25863-2025</t>
+          <t>A 39988-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45804</v>
+        <v>45553</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33875-2024</t>
+          <t>A 56145-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45521</v>
+        <v>44889</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>14.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59503-2024</t>
+          <t>A 25863-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45638</v>
+        <v>45804</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6301,7 +6301,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 42155-2025</t>
+          <t>A 33875-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45904</v>
+        <v>45521</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6330,13 +6330,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6379,7 +6374,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39988-2024</t>
+          <t>A 6196-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6393,10 +6388,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45553</v>
+        <v>44964</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6409,7 +6404,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6452,7 +6447,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6690-2023</t>
+          <t>A 42155-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6466,10 +6461,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44966</v>
+        <v>45904</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6481,8 +6476,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6525,7 +6525,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43134-2025</t>
+          <t>A 3775-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45909</v>
+        <v>45321</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6598,7 +6598,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28942-2025</t>
+          <t>A 57500-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45820</v>
+        <v>44896</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6671,7 +6671,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15707-2025</t>
+          <t>A 14226-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45748</v>
+        <v>45393</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6744,7 +6744,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40157-2023</t>
+          <t>A 1347-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45169</v>
+        <v>46031</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35113-2024</t>
+          <t>A 43134-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45529</v>
+        <v>45909</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6890,7 +6890,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 46536-2025</t>
+          <t>A 28942-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6904,10 +6904,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45926</v>
+        <v>45820</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6963,7 +6963,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46539-2025</t>
+          <t>A 46533-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6980,7 +6980,7 @@
         <v>45926</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46533-2025</t>
+          <t>A 46539-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7053,7 +7053,7 @@
         <v>45926</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46848-2025</t>
+          <t>A 16349-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45928</v>
+        <v>44670</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48096-2025</t>
+          <t>A 39990-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45933</v>
+        <v>45553</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7255,7 +7255,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4438-2025</t>
+          <t>A 46536-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45686</v>
+        <v>45926</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7328,7 +7328,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49779-2025</t>
+          <t>A 46848-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45940</v>
+        <v>45928</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7401,7 +7401,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30641-2024</t>
+          <t>A 48096-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45495</v>
+        <v>45933</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52321-2025</t>
+          <t>A 14748-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45953</v>
+        <v>44656</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 27549-2022</t>
+          <t>A 49779-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44742</v>
+        <v>45940</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1347-2026</t>
+          <t>A 21687-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46031</v>
+        <v>44707</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 49733-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45702</v>
+        <v>45596</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>15.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37131-2025</t>
+          <t>A 58712-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45875</v>
+        <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37133-2025</t>
+          <t>A 12273-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45875</v>
+        <v>44998</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37427-2025</t>
+          <t>A 37131-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45877</v>
+        <v>45875</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37424-2025</t>
+          <t>A 37133-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7999,10 +7999,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45877</v>
+        <v>45875</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8058,7 +8058,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19107-2023</t>
+          <t>A 52321-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45048</v>
+        <v>45953</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8131,7 +8131,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 6196-2023</t>
+          <t>A 37427-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44964</v>
+        <v>45877</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 6208-2023</t>
+          <t>A 37424-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44964</v>
+        <v>45877</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49733-2024</t>
+          <t>A 59503-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45596</v>
+        <v>45638</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>15.1</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 39990-2024</t>
+          <t>A 8371-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45553</v>
+        <v>44977</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14226-2024</t>
+          <t>A 47860-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8433,14 +8433,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45393</v>
+        <v>45204</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8496,7 +8496,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 57500-2022</t>
+          <t>A 49734-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44896</v>
+        <v>45596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2642-2025</t>
+          <t>A 12351-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8579,14 +8579,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45676</v>
+        <v>46088</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20671-2022</t>
+          <t>A 62586-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8652,14 +8652,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44700</v>
+        <v>46007</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12351-2026</t>
+          <t>A 62956-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8725,14 +8725,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46088</v>
+        <v>46009</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8788,7 +8788,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 22270-2024</t>
+          <t>A 15707-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45446</v>
+        <v>45748</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6194-2023</t>
+          <t>A 16573-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8871,14 +8871,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44964</v>
+        <v>45752</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8934,7 +8934,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6214-2023</t>
+          <t>A 40960-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44964</v>
+        <v>45169</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49925-2023</t>
+          <t>A 57423-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45214</v>
+        <v>45246</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28605-2023</t>
+          <t>A 15189-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45103</v>
+        <v>45016</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35244-2023</t>
+          <t>A 50297-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45145</v>
+        <v>44865</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17007-2025</t>
+          <t>A 16567-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45755</v>
+        <v>45752</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17011-2025</t>
+          <t>A 16568-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45755</v>
+        <v>45752</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 16567-2025</t>
+          <t>A 16570-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9389,7 +9389,7 @@
         <v>45752</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16568-2025</t>
+          <t>A 18421-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9455,14 +9455,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45752</v>
+        <v>46126</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 16570-2025</t>
+          <t>A 30641-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45752</v>
+        <v>45495</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 46901-2023</t>
+          <t>A 2495-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45201</v>
+        <v>45313</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 18421-2026</t>
+          <t>A 4355-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9674,14 +9674,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46126</v>
+        <v>44954</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 40960-2023</t>
+          <t>A 11117-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45169</v>
+        <v>44992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8371-2023</t>
+          <t>A 7654-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44977</v>
+        <v>44607</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9883,7 +9883,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16573-2025</t>
+          <t>A 28940-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9893,14 +9893,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45752</v>
+        <v>45820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9956,7 +9956,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 7654-2022</t>
+          <t>A 1794-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44607</v>
+        <v>44938</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10029,7 +10029,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16350-2022</t>
+          <t>A 35245-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10043,10 +10043,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44670</v>
+        <v>45145</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 2495-2024</t>
+          <t>A 12423-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45313</v>
+        <v>45730</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10175,7 +10175,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28940-2025</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45820</v>
+        <v>45048</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10248,7 +10248,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 12423-2025</t>
+          <t>A 15489-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10262,10 +10262,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45730</v>
+        <v>45401</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 59332-2024</t>
+          <t>A 37797-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45637</v>
+        <v>45543</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 23787-2024</t>
+          <t>A 37798-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45455</v>
+        <v>45543</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 24566-2023</t>
+          <t>A 16571-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45083</v>
+        <v>45752</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>13.1</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10540,7 +10540,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 11515-2024</t>
+          <t>A 24566-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45372</v>
+        <v>45083</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10569,13 +10569,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>7.2</v>
+        <v>13.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10618,7 +10613,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14064-2025</t>
+          <t>A 35244-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10632,10 +10627,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45740</v>
+        <v>45145</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10648,7 +10643,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10691,7 +10686,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7181-2023</t>
+          <t>A 46901-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10705,10 +10700,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44970</v>
+        <v>45201</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10720,13 +10715,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10765,31 +10755,11 @@
         <v>0</v>
       </c>
       <c r="V126" s="2" t="inlineStr"/>
-      <c r="Z126">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AA126">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AB126">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AC126">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
-      <c r="AD126">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4355-2023</t>
+          <t>A 40661-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10803,10 +10773,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44954</v>
+        <v>45170</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10819,7 +10789,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10862,7 +10832,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 2497-2024</t>
+          <t>A 11282-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10876,10 +10846,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45313</v>
+        <v>45371</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10892,7 +10862,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10935,7 +10905,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 14748-2022</t>
+          <t>A 3837-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10949,10 +10919,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44656</v>
+        <v>45682</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10965,7 +10935,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11008,7 +10978,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 40157-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11022,10 +10992,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44817</v>
+        <v>45169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11038,7 +11008,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11081,7 +11051,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 57025-2022</t>
+          <t>A 4438-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11095,10 +11065,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44895</v>
+        <v>45686</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11111,7 +11081,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11154,7 +11124,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 23789-2024</t>
+          <t>A 14742-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11168,10 +11138,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45455</v>
+        <v>44656</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11184,7 +11154,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11227,7 +11197,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52385-2022</t>
+          <t>A 14745-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11241,10 +11211,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44869</v>
+        <v>44656</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11257,7 +11227,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11300,7 +11270,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56145-2022</t>
+          <t>A 49925-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11314,10 +11284,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44889</v>
+        <v>45214</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11330,7 +11300,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>14.1</v>
+        <v>0.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11373,7 +11343,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 4356-2023</t>
+          <t>A 59332-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11387,10 +11357,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44954</v>
+        <v>45637</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11403,7 +11373,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11446,7 +11416,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4359-2023</t>
+          <t>A 16350-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11460,10 +11430,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44954</v>
+        <v>44670</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11476,7 +11446,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11519,7 +11489,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12273-2023</t>
+          <t>A 14064-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11529,14 +11499,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44998</v>
+        <v>45740</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11549,7 +11519,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11592,7 +11562,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 50297-2022</t>
+          <t>A 34914-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11606,10 +11576,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44865</v>
+        <v>44796</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11622,7 +11592,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11665,7 +11635,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11457-2023</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11679,10 +11649,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44993</v>
+        <v>45372</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11694,8 +11664,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11738,7 +11713,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 56876-2023</t>
+          <t>A 2497-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11748,14 +11723,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45244</v>
+        <v>45313</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11768,7 +11743,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11811,7 +11786,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 28508-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11825,10 +11800,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45702</v>
+        <v>46197</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11841,7 +11816,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11901,7 +11876,7 @@
         <v>46197</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11957,7 +11932,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28508-2026</t>
+          <t>A 6690-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11971,10 +11946,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46197</v>
+        <v>44966</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11987,7 +11962,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12030,7 +12005,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 1794-2023</t>
+          <t>A 28791-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12040,14 +12015,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44938</v>
+        <v>45478</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12060,7 +12035,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12103,7 +12078,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34914-2022</t>
+          <t>A 11281-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12117,10 +12092,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44796</v>
+        <v>45371</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12133,7 +12108,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12176,7 +12151,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 14742-2022</t>
+          <t>A 4356-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12190,10 +12165,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44656</v>
+        <v>44954</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12206,7 +12181,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12249,7 +12224,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14745-2022</t>
+          <t>A 11457-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12263,10 +12238,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44656</v>
+        <v>44993</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12279,7 +12254,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12322,7 +12297,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26757-2024</t>
+          <t>A 6194-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12336,10 +12311,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45469</v>
+        <v>44964</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12352,7 +12327,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12395,7 +12370,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 42872-2022</t>
+          <t>A 23128-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12405,14 +12380,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44832</v>
+        <v>45450</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12425,7 +12400,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12468,7 +12443,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3775-2024</t>
+          <t>A 7181-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12482,10 +12457,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45321</v>
+        <v>44970</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12497,8 +12472,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12537,11 +12517,31 @@
         <v>0</v>
       </c>
       <c r="V150" s="2" t="inlineStr"/>
+      <c r="Z150">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 7181-2023 karta knärot.png", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AA150">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7181-2023 FSC-klagomål.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AB150">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7181-2023 FSC-klagomål mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AC150">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7181-2023 tillsynsbegäran.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
+      <c r="AD150">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7181-2023 tillsynsbegäran mail.docx", "A 7181-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 40661-2023</t>
+          <t>A 28605-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45170</v>
+        <v>45103</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12614,7 +12614,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31162-2026</t>
+          <t>A 71048-2021</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12628,10 +12628,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46216</v>
+        <v>44538</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12687,7 +12687,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 31157-2026</t>
+          <t>A 56876-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12697,14 +12697,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46216</v>
+        <v>45244</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12760,7 +12760,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 15489-2024</t>
+          <t>A 31157-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45401</v>
+        <v>46216</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12833,7 +12833,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 11117-2023</t>
+          <t>A 23789-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44992</v>
+        <v>45455</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 35115-2026</t>
+          <t>A 31162-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46260</v>
+        <v>46216</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 11282-2024</t>
+          <t>A 4359-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45371</v>
+        <v>44954</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13052,7 +13052,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 3946-2023</t>
+          <t>A 6208-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13066,10 +13066,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44952</v>
+        <v>44964</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13125,7 +13125,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 47860-2023</t>
+          <t>A 35115-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13139,10 +13139,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45204</v>
+        <v>46260</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 36412-2026</t>
+          <t>A 17007-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46268</v>
+        <v>45755</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13271,7 +13271,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36414-2026</t>
+          <t>A 17011-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46268</v>
+        <v>45755</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13344,7 +13344,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 23128-2024</t>
+          <t>A 36412-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45450</v>
+        <v>46268</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13434,7 +13434,7 @@
         <v>46268</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15189-2023</t>
+          <t>A 22270-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13504,10 +13504,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45016</v>
+        <v>45446</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13563,7 +13563,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 16571-2025</t>
+          <t>A 36414-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45752</v>
+        <v>46268</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13636,7 +13636,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 58712-2023</t>
+          <t>A 2642-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45251</v>
+        <v>45676</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 16349-2022</t>
+          <t>A 31984-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44670</v>
+        <v>46232</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13782,7 +13782,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31984-2026</t>
+          <t>A 37124-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13792,14 +13792,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46232</v>
+        <v>46274</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13855,7 +13855,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 11281-2024</t>
+          <t>A 32702-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13869,10 +13869,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45371</v>
+        <v>46240</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 57423-2023</t>
+          <t>A 32699-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45246</v>
+        <v>46240</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14001,7 +14001,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37124-2026</t>
+          <t>A 27549-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14011,14 +14011,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46274</v>
+        <v>44742</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14074,7 +14074,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 64387-2023</t>
+          <t>A 20671-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45280</v>
+        <v>44700</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14147,7 +14147,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 4252-2024</t>
+          <t>A 3946-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14161,10 +14161,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45324</v>
+        <v>44952</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 32702-2026</t>
+          <t>A 33296-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 32699-2026</t>
+          <t>A 64387-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14307,10 +14307,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46240</v>
+        <v>45280</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 4957-2022</t>
+          <t>A 4252-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44593</v>
+        <v>45324</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14439,7 +14439,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 33275-2026</t>
+          <t>A 4957-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14453,10 +14453,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46246</v>
+        <v>44593</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14512,7 +14512,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 33296-2026</t>
+          <t>A 33275-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14529,7 +14529,7 @@
         <v>46246</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14602,7 +14602,7 @@
         <v>46293</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45524</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45587</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45763</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>

--- a/Översikt MULLSJÖ.xlsx
+++ b/Översikt MULLSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE182"/>
+  <dimension ref="A1:AE183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45735</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45355</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>45396</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45751</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45173</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7821-2024</t>
+          <t>A 35828-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45349</v>
+        <v>45532</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1354,375 +1354,375 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Sommarfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 45507-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45578</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Knärot
+Lönnlav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 7821-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Slåtterfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7821-2024 artfynd.xlsx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7821-2024 karta.png", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7821-2024 georefererad karta.tif", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7821-2024 FSC-klagomål.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7821-2024 FSC-klagomål mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7821-2024 tillsynsbegäran.docx", "A 7821-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7821-2024 tillsynsbegäran mail.docx", "A 7821-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 35828-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45532</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 37686-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sommarfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 35828-2024 artfynd.xlsx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 35828-2024 karta.png", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 35828-2024 georefererad karta.tif", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 35828-2024 FSC-klagomål.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 35828-2024 FSC-klagomål mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 35828-2024 tillsynsbegäran.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 35828-2024 tillsynsbegäran mail.docx", "A 35828-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 37686-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Sommarfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 37686-2026 artfynd.xlsx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 37686-2026 karta.png", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 37686-2026 georefererad karta.tif", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 37686-2026 FSC-klagomål.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 37686-2026 FSC-klagomål mail.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 37686-2026 tillsynsbegäran.docx", "A 37686-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 37686-2026 tillsynsbegäran mail.docx", "A 37686-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 45507-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45578</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Knärot
-Lönnlav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 45507-2024 artfynd.xlsx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 45507-2024 karta.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 45507-2024 georefererad karta.tif", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 45507-2024 karta knärot.png", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 45507-2024 FSC-klagomål.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 45507-2024 FSC-klagomål mail.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 45507-2024 tillsynsbegäran.docx", "A 45507-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 45507-2024 tillsynsbegäran mail.docx", "A 45507-2024")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>44476</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7817-2024</t>
+          <t>A 7365-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45349</v>
+        <v>44971</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1869,22 +1869,22 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.9</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1893,10 +1893,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -1909,142 +1909,142 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Fläcknycklar
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7365-2023 artfynd.xlsx", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7365-2023 karta.png", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7365-2023 georefererad karta.tif", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7365-2023 FSC-klagomål.docx", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7365-2023 FSC-klagomål mail.docx", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7365-2023 tillsynsbegäran.docx", "A 7365-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7365-2023 tillsynsbegäran mail.docx", "A 7365-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 7817-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MULLSJÖ</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Huskvarnafibbla</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7817-2024 artfynd.xlsx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7817-2024 karta.png", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7817-2024 georefererad karta.tif", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7817-2024 FSC-klagomål.docx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7817-2024 FSC-klagomål mail.docx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7817-2024 tillsynsbegäran.docx", "A 7817-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7817-2024 tillsynsbegäran mail.docx", "A 7817-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 7365-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44971</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MULLSJÖ</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7365-2023 artfynd.xlsx", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7365-2023 karta.png", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7365-2023 georefererad karta.tif", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7365-2023 FSC-klagomål.docx", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7365-2023 FSC-klagomål mail.docx", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7365-2023 tillsynsbegäran.docx", "A 7365-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7365-2023 tillsynsbegäran mail.docx", "A 7365-2023")</f>
         <v/>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46006-2022</t>
+          <t>A 14230-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44846</v>
+        <v>45393</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,19 +2300,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2336,46 +2336,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 44654-2023</t>
+          <t>A 13882-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45189</v>
+        <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2404,25 +2404,20 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2434,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2450,42 +2445,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 56244-2022</t>
+          <t>A 62232-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2499,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44890</v>
+        <v>44922</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,29 +2509,24 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
@@ -2544,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2556,46 +2546,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1221-2026</t>
+          <t>A 7823-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2605,14 +2595,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46031</v>
+        <v>45349</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2624,13 +2614,8 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2663,49 +2648,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7823-2024</t>
+          <t>A 57195-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2715,14 +2700,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45349</v>
+        <v>45629</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2734,8 +2719,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2775,42 +2765,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 7823-2024 artfynd.xlsx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 7823-2024 karta.png", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 7823-2024 georefererad karta.tif", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 7823-2024 FSC-klagomål.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 7823-2024 FSC-klagomål mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 7823-2024 tillsynsbegäran.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 7823-2024 tillsynsbegäran mail.docx", "A 7823-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 62232-2022</t>
+          <t>A 44654-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2824,10 +2814,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44922</v>
+        <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2839,8 +2829,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2852,10 +2847,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2876,46 +2871,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 62232-2022 artfynd.xlsx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 44654-2023 artfynd.xlsx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 62232-2022 karta.png", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 44654-2023 karta.png", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 62232-2022 georefererad karta.tif", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 44654-2023 georefererad karta.tif", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 62232-2022 FSC-klagomål.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 44654-2023 FSC-klagomål.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 62232-2022 FSC-klagomål mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 44654-2023 FSC-klagomål mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 62232-2022 tillsynsbegäran.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 44654-2023 tillsynsbegäran.docx", "A 44654-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 62232-2022 tillsynsbegäran mail.docx", "A 62232-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 44654-2023 tillsynsbegäran mail.docx", "A 44654-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15498-2024</t>
+          <t>A 46006-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2929,10 +2924,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45401</v>
+        <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2944,16 +2939,11 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2990,46 +2980,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 46006-2022 artfynd.xlsx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 46006-2022 karta.png", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 46006-2022 georefererad karta.tif", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 46006-2022 FSC-klagomål.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 46006-2022 FSC-klagomål mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 46006-2022 tillsynsbegäran.docx", "A 46006-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 46006-2022 tillsynsbegäran mail.docx", "A 46006-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55693-2025</t>
+          <t>A 15498-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,14 +3025,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45972</v>
+        <v>45401</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3058,11 +3044,16 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3071,10 +3062,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3092,49 +3083,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 15498-2024 artfynd.xlsx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 15498-2024 karta.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 15498-2024 georefererad karta.tif", "A 15498-2024")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/knärot/A 15498-2024 karta knärot.png", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 15498-2024 FSC-klagomål.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 15498-2024 FSC-klagomål mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 15498-2024 tillsynsbegäran.docx", "A 15498-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 15498-2024 tillsynsbegäran mail.docx", "A 15498-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17825-2026</t>
+          <t>A 55693-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3144,14 +3139,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46122</v>
+        <v>45972</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,23 +3159,23 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3188,58 +3183,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 55693-2025 artfynd.xlsx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 55693-2025 karta.png", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 55693-2025 georefererad karta.tif", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 55693-2025 FSC-klagomål.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 55693-2025 FSC-klagomål mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 55693-2025 tillsynsbegäran.docx", "A 55693-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 55693-2025 tillsynsbegäran mail.docx", "A 55693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 14230-2024</t>
+          <t>A 1221-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3249,14 +3244,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45393</v>
+        <v>46031</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3268,18 +3263,23 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3302,49 +3302,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 14230-2024 artfynd.xlsx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 1221-2026 artfynd.xlsx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 14230-2024 karta.png", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 1221-2026 karta.png", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 14230-2024 georefererad karta.tif", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 1221-2026 georefererad karta.tif", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 14230-2024 FSC-klagomål.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 1221-2026 FSC-klagomål.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 14230-2024 FSC-klagomål mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 1221-2026 FSC-klagomål mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 14230-2024 tillsynsbegäran.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 1221-2026 tillsynsbegäran.docx", "A 1221-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 14230-2024 tillsynsbegäran mail.docx", "A 14230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 1221-2026 tillsynsbegäran mail.docx", "A 1221-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57195-2024</t>
+          <t>A 56244-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45629</v>
+        <v>44890</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3375,20 +3375,20 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3415,46 +3415,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 57195-2024 artfynd.xlsx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 56244-2022 artfynd.xlsx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 57195-2024 karta.png", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 56244-2022 karta.png", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 57195-2024 georefererad karta.tif", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 56244-2022 georefererad karta.tif", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 57195-2024 FSC-klagomål.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 56244-2022 FSC-klagomål.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 57195-2024 FSC-klagomål mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 56244-2022 FSC-klagomål mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 57195-2024 tillsynsbegäran.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 56244-2022 tillsynsbegäran.docx", "A 56244-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 57195-2024 tillsynsbegäran mail.docx", "A 57195-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 56244-2022 tillsynsbegäran mail.docx", "A 56244-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13882-2023</t>
+          <t>A 17825-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3464,14 +3464,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45007</v>
+        <v>46122</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3484,13 +3484,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3517,42 +3517,42 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 13882-2023 artfynd.xlsx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/artfynd/A 17825-2026 artfynd.xlsx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 13882-2023 karta.png", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor/A 17825-2026 karta.png", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 13882-2023 georefererad karta.tif", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/kartor_geotiff/A 17825-2026 georefererad karta.tif", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 13882-2023 FSC-klagomål.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomål/A 17825-2026 FSC-klagomål.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 13882-2023 FSC-klagomål mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/klagomålsmail/A 17825-2026 FSC-klagomål mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 13882-2023 tillsynsbegäran.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsyn/A 17825-2026 tillsynsbegäran.docx", "A 17825-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 13882-2023 tillsynsbegäran mail.docx", "A 13882-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0642/tillsynsmail/A 17825-2026 tillsynsbegäran mail.docx", "A 17825-2026")</f>
         <v/>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>44516</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57229-2021</t>
+          <t>A 9903-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44483</v>
+        <v>44620</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>16.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9903-2022</t>
+          <t>A 57229-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44620</v>
+        <v>44483</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>16.8</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13811-2022</t>
+          <t>A 27760-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44649</v>
+        <v>44743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4330,7 +4330,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62452-2021</t>
+          <t>A 13811-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44503</v>
+        <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27760-2022</t>
+          <t>A 62452-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44743</v>
+        <v>44503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21691-2022</t>
+          <t>A 7278-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44707</v>
+        <v>45702</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4549,7 +4549,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16133-2022</t>
+          <t>A 21691-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44665</v>
+        <v>44707</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21693-2022</t>
+          <t>A 16133-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44707</v>
+        <v>44665</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4695,7 +4695,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7278-2025</t>
+          <t>A 21693-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45702</v>
+        <v>44707</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 39353-2022</t>
+          <t>A 11515-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44817</v>
+        <v>45372</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4797,8 +4797,13 @@
           <t>MULLSJÖ</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4841,7 +4846,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7268-2025</t>
+          <t>A 19107-2023</t>
         </is>
       </c>
       <c r="B46" t="inl